--- a/lookup/Spill_lab_tracking.xlsx
+++ b/lookup/Spill_lab_tracking.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/Projects/refactor/lookup/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/refactor/lookup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1959" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74A3FAAE-2A0B-4145-89A9-38418A29D3E8}"/>
+  <xr:revisionPtr revIDLastSave="2002" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4265AB0E-99B5-46B2-A702-058D04E22A09}"/>
   <bookViews>
-    <workbookView xWindow="5250" yWindow="2220" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
+    <workbookView xWindow="2340" yWindow="456" windowWidth="19668" windowHeight="11136" activeTab="1" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
     <sheet name="sites" sheetId="7" r:id="rId2"/>
     <sheet name="Contacts" sheetId="8" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="789">
   <si>
     <t>Durham</t>
   </si>
@@ -2140,9 +2140,6 @@
     <t>RP: Tennet: Catherine Mathews (cemathews98@gmail.com; 207-373-8350)</t>
   </si>
   <si>
-    <t>probably won't call; will call to discuss closure</t>
-  </si>
-  <si>
     <t>DaytonLF</t>
   </si>
   <si>
@@ -2164,9 +2161,6 @@
     <t>L2624524-01</t>
   </si>
   <si>
-    <t>mail as one packet with resample</t>
-  </si>
-  <si>
     <t>L2623914-01</t>
   </si>
   <si>
@@ -2356,12 +2350,6 @@
     <t>kondo</t>
   </si>
   <si>
-    <t>eph</t>
-  </si>
-  <si>
-    <t>vph</t>
-  </si>
-  <si>
     <t>L2648717-01</t>
   </si>
   <si>
@@ -2399,6 +2387,24 @@
   </si>
   <si>
     <t>L2649652-02</t>
+  </si>
+  <si>
+    <t>did not report</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Casco</t>
+  </si>
+  <si>
+    <t>P-689-2007</t>
+  </si>
+  <si>
+    <t>H:\BRWM\BRWM Databases\FILE ROOM\TechServSpillClosure\SMRO\Casco Chase Bank P-689-2007</t>
+  </si>
+  <si>
+    <t>Chase Bank</t>
   </si>
 </sst>
 </file>
@@ -2408,7 +2414,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2491,8 +2497,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2505,8 +2516,14 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2555,17 +2572,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2574,7 +2580,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2674,9 +2680,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2686,6 +2689,10 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
@@ -2694,7 +2701,14 @@
     <cellStyle name="Normal 3" xfId="3" xr:uid="{7DD157AA-FB4C-450F-AAF2-4C4F84CD4C39}"/>
     <cellStyle name="Some Sampled" xfId="1" xr:uid="{6BE03E6A-B30A-4007-8EF9-ECB03A2DC2CB}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3033,24 +3047,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9741DC-F95F-47C4-8FE8-2842B1A8CB0D}">
   <dimension ref="A1:L147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="16" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" customWidth="1"/>
     <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="23"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" style="23"/>
+    <col min="12" max="12" width="11.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="7" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -3081,9 +3095,9 @@
       <c r="J1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="38"/>
-    </row>
-    <row r="2" spans="1:11" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="37"/>
+    </row>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>98</v>
       </c>
@@ -3114,9 +3128,9 @@
       <c r="J2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="38"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K2" s="37"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>98</v>
       </c>
@@ -3148,7 +3162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>98</v>
       </c>
@@ -3180,7 +3194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>98</v>
       </c>
@@ -3212,7 +3226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>98</v>
       </c>
@@ -3244,7 +3258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>432</v>
       </c>
@@ -3276,7 +3290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>432</v>
       </c>
@@ -3308,7 +3322,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>98</v>
       </c>
@@ -3340,7 +3354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
@@ -3372,7 +3386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>66</v>
       </c>
@@ -3380,7 +3394,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D11" s="34">
         <v>45747</v>
@@ -3404,7 +3418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
@@ -3436,7 +3450,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>98</v>
       </c>
@@ -3468,7 +3482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>589</v>
       </c>
@@ -3500,7 +3514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
@@ -3532,7 +3546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>589</v>
       </c>
@@ -3564,7 +3578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>589</v>
       </c>
@@ -3596,7 +3610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>589</v>
       </c>
@@ -3628,7 +3642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
@@ -3660,7 +3674,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
@@ -3692,7 +3706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>11</v>
       </c>
@@ -3724,7 +3738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>86</v>
       </c>
@@ -3756,7 +3770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>86</v>
       </c>
@@ -3788,7 +3802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>86</v>
       </c>
@@ -3820,7 +3834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>29</v>
       </c>
@@ -3852,7 +3866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
@@ -3884,7 +3898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>18</v>
       </c>
@@ -3916,7 +3930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
@@ -3948,7 +3962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>589</v>
       </c>
@@ -3980,7 +3994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>589</v>
       </c>
@@ -4012,7 +4026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>50</v>
       </c>
@@ -4044,7 +4058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>62</v>
       </c>
@@ -4076,7 +4090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>63</v>
       </c>
@@ -4108,7 +4122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>66</v>
       </c>
@@ -4116,7 +4130,7 @@
         <v>79</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D34" s="34">
         <v>45845</v>
@@ -4140,7 +4154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>66</v>
       </c>
@@ -4148,7 +4162,7 @@
         <v>80</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D35" s="34">
         <v>45845</v>
@@ -4172,7 +4186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>66</v>
       </c>
@@ -4204,7 +4218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>73</v>
       </c>
@@ -4236,7 +4250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>62</v>
       </c>
@@ -4268,7 +4282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>63</v>
       </c>
@@ -4300,7 +4314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>62</v>
       </c>
@@ -4332,7 +4346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>11</v>
       </c>
@@ -4364,7 +4378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>11</v>
       </c>
@@ -4396,7 +4410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>11</v>
       </c>
@@ -4428,7 +4442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>86</v>
       </c>
@@ -4460,7 +4474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>86</v>
       </c>
@@ -4492,7 +4506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>86</v>
       </c>
@@ -4524,7 +4538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>332</v>
       </c>
@@ -4556,7 +4570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>332</v>
       </c>
@@ -4588,7 +4602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>29</v>
       </c>
@@ -4620,7 +4634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>589</v>
       </c>
@@ -4652,7 +4666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>32</v>
       </c>
@@ -4684,7 +4698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>49</v>
       </c>
@@ -4716,7 +4730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>63</v>
       </c>
@@ -4748,7 +4762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>73</v>
       </c>
@@ -4780,7 +4794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>66</v>
       </c>
@@ -4813,7 +4827,7 @@
       </c>
       <c r="L55" s="15"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>62</v>
       </c>
@@ -4845,7 +4859,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>50</v>
       </c>
@@ -4877,7 +4891,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>11</v>
       </c>
@@ -4909,7 +4923,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>11</v>
       </c>
@@ -4941,7 +4955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>11</v>
       </c>
@@ -4976,7 +4990,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>476</v>
       </c>
@@ -5011,7 +5025,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>476</v>
       </c>
@@ -5043,7 +5057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5075,7 +5089,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>589</v>
       </c>
@@ -5107,7 +5121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>32</v>
       </c>
@@ -5139,7 +5153,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>86</v>
       </c>
@@ -5171,7 +5185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>86</v>
       </c>
@@ -5203,7 +5217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>63</v>
       </c>
@@ -5235,7 +5249,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>66</v>
       </c>
@@ -5267,7 +5281,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>216</v>
       </c>
@@ -5300,7 +5314,7 @@
       </c>
       <c r="K70"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>216</v>
       </c>
@@ -5332,7 +5346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>219</v>
       </c>
@@ -5364,7 +5378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>220</v>
       </c>
@@ -5396,7 +5410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>218</v>
       </c>
@@ -5406,7 +5420,7 @@
       <c r="C74" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="D74" s="40">
+      <c r="D74" s="39">
         <v>45918</v>
       </c>
       <c r="E74" s="4" t="s">
@@ -5428,7 +5442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>345</v>
       </c>
@@ -5438,7 +5452,7 @@
       <c r="C75" s="36" t="s">
         <v>547</v>
       </c>
-      <c r="D75" s="40">
+      <c r="D75" s="39">
         <v>45966</v>
       </c>
       <c r="E75" s="4" t="s">
@@ -5460,7 +5474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>213</v>
       </c>
@@ -5492,7 +5506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>213</v>
       </c>
@@ -5524,7 +5538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>213</v>
       </c>
@@ -5556,7 +5570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>213</v>
       </c>
@@ -5588,7 +5602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>211</v>
       </c>
@@ -5620,7 +5634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>211</v>
       </c>
@@ -5652,7 +5666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>217</v>
       </c>
@@ -5684,7 +5698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>217</v>
       </c>
@@ -5716,7 +5730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>217</v>
       </c>
@@ -5748,7 +5762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>217</v>
       </c>
@@ -5780,7 +5794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>29</v>
       </c>
@@ -5812,7 +5826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>11</v>
       </c>
@@ -5844,7 +5858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>11</v>
       </c>
@@ -5876,7 +5890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>11</v>
       </c>
@@ -5908,7 +5922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>62</v>
       </c>
@@ -5940,7 +5954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>576</v>
       </c>
@@ -5972,7 +5986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>50</v>
       </c>
@@ -6004,7 +6018,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>32</v>
       </c>
@@ -6036,7 +6050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>461</v>
       </c>
@@ -6068,7 +6082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>461</v>
       </c>
@@ -6100,7 +6114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>461</v>
       </c>
@@ -6132,7 +6146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>621</v>
       </c>
@@ -6164,9 +6178,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B98" s="30" t="s">
         <v>684</v>
@@ -6196,9 +6210,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B99" s="30" t="s">
         <v>687</v>
@@ -6228,12 +6242,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>635</v>
@@ -6260,7 +6274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>86</v>
       </c>
@@ -6292,7 +6306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>86</v>
       </c>
@@ -6324,7 +6338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>86</v>
       </c>
@@ -6352,12 +6366,12 @@
       <c r="I103" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J103" s="4"/>
-      <c r="K103" s="37" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J103" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K103"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>642</v>
       </c>
@@ -6389,7 +6403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>642</v>
       </c>
@@ -6414,23 +6428,22 @@
       <c r="H105" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I105" s="4"/>
+      <c r="I105" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="J105" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K105" s="23" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>642</v>
       </c>
       <c r="B106" s="30" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D106" s="34">
         <v>46135</v>
@@ -6447,23 +6460,22 @@
       <c r="H106" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I106" s="4"/>
+      <c r="I106" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="J106" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K106" s="23" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>642</v>
       </c>
       <c r="B107" s="30" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D107" s="34">
         <v>46135</v>
@@ -6480,20 +6492,19 @@
       <c r="H107" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I107" s="4"/>
+      <c r="I107" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="J107" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K107" s="23" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B108" s="30" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>385</v>
@@ -6520,12 +6531,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B109" s="30" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>70</v>
@@ -6548,9 +6559,14 @@
       <c r="I109" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J109" s="4"/>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J109" s="40" t="s">
+        <v>784</v>
+      </c>
+      <c r="K109" s="23" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>642</v>
       </c>
@@ -6582,12 +6598,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>642</v>
       </c>
       <c r="B111" s="30" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>639</v>
@@ -6607,18 +6623,19 @@
       <c r="H111" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
-      <c r="K111" s="23" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I111" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B112" s="30" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>72</v>
@@ -6645,15 +6662,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B113" s="30" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D113" s="34">
         <v>46147</v>
@@ -6670,18 +6687,22 @@
       <c r="H113" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
+      <c r="I113" s="40" t="s">
+        <v>784</v>
+      </c>
+      <c r="J113" s="40" t="s">
+        <v>784</v>
+      </c>
       <c r="K113" s="23" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>621</v>
       </c>
       <c r="B114" s="30" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>623</v>
@@ -6708,12 +6729,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>642</v>
       </c>
       <c r="B115" s="30" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>639</v>
@@ -6740,12 +6761,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B116" s="30" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>385</v>
@@ -6772,12 +6793,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>642</v>
       </c>
       <c r="B117" s="30" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>639</v>
@@ -6788,21 +6809,26 @@
       <c r="E117" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
-      <c r="I117" s="4"/>
+      <c r="F117" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="J117" s="4"/>
-      <c r="K117" s="23" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>642</v>
       </c>
       <c r="B118" s="30" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>639</v>
@@ -6813,24 +6839,29 @@
       <c r="E118" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
-      <c r="I118" s="4"/>
+      <c r="F118" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="J118" s="4"/>
-      <c r="K118" s="23" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>642</v>
       </c>
       <c r="B119" s="30" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D119" s="34">
         <v>46237</v>
@@ -6838,21 +6869,29 @@
       <c r="E119" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
+      <c r="F119" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="J119" s="4"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>642</v>
       </c>
       <c r="B120" s="30" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D120" s="34">
         <v>46237</v>
@@ -6860,13 +6899,21 @@
       <c r="E120" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F120" s="4"/>
-      <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="4"/>
+      <c r="F120" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I120" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="J120" s="4"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="30"/>
       <c r="D121" s="34"/>
@@ -6877,7 +6924,7 @@
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="30"/>
       <c r="D122" s="34"/>
@@ -6888,7 +6935,7 @@
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="30"/>
       <c r="D123" s="34"/>
@@ -6899,7 +6946,7 @@
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="30"/>
       <c r="D124" s="34"/>
@@ -6910,7 +6957,7 @@
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="30"/>
       <c r="D125" s="34"/>
@@ -6921,7 +6968,7 @@
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="30"/>
       <c r="D126" s="34"/>
@@ -6932,7 +6979,7 @@
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="30"/>
       <c r="D127" s="34"/>
@@ -6943,7 +6990,7 @@
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="30"/>
       <c r="D128" s="34"/>
@@ -6954,7 +7001,7 @@
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="30"/>
       <c r="D129" s="34"/>
@@ -6965,7 +7012,7 @@
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="30"/>
       <c r="D130" s="34"/>
@@ -6976,7 +7023,7 @@
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="30"/>
       <c r="D131" s="34"/>
@@ -6987,7 +7034,7 @@
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="30"/>
       <c r="D132" s="34"/>
@@ -6998,7 +7045,7 @@
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="30"/>
       <c r="D133" s="34"/>
@@ -7009,7 +7056,7 @@
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="30"/>
       <c r="D134" s="34"/>
@@ -7020,7 +7067,7 @@
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="30"/>
       <c r="D135" s="34"/>
@@ -7031,7 +7078,7 @@
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="30"/>
       <c r="D136" s="34"/>
@@ -7042,7 +7089,7 @@
       <c r="I136" s="4"/>
       <c r="J136" s="4"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="30"/>
       <c r="D137" s="34"/>
@@ -7053,7 +7100,7 @@
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="30"/>
       <c r="D138" s="34"/>
@@ -7064,7 +7111,7 @@
       <c r="I138" s="4"/>
       <c r="J138" s="4"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="30"/>
       <c r="D139" s="34"/>
@@ -7075,7 +7122,7 @@
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="30"/>
       <c r="D140" s="34"/>
@@ -7086,7 +7133,7 @@
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="30"/>
       <c r="D141" s="34"/>
@@ -7097,7 +7144,7 @@
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="30"/>
       <c r="D142" s="34"/>
@@ -7108,7 +7155,7 @@
       <c r="I142" s="4"/>
       <c r="J142" s="4"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="30"/>
       <c r="D143" s="34"/>
@@ -7119,7 +7166,7 @@
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="30"/>
       <c r="D144" s="34"/>
@@ -7130,7 +7177,7 @@
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="30"/>
       <c r="D145" s="34"/>
@@ -7141,7 +7188,7 @@
       <c r="I145" s="4"/>
       <c r="J145" s="4"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="30"/>
       <c r="D146" s="34"/>
@@ -7152,7 +7199,7 @@
       <c r="I146" s="4"/>
       <c r="J146" s="4"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="30"/>
       <c r="D147" s="34"/>
@@ -7165,12 +7212,17 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="E2:J147 K103">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="X">
+  <conditionalFormatting sqref="E2:J147">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",E2)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="0" priority="2">
+    <cfRule type="containsBlanks" dxfId="1" priority="3">
       <formula>LEN(TRIM(E2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E113:J147">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7180,22 +7232,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05C0069-E32D-47E3-8952-41BB91A7FDEB}">
-  <dimension ref="A1:L100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L101"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="11"/>
-    <col min="8" max="8" width="8.85546875" style="9"/>
+    <col min="5" max="5" width="7.109375" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="11"/>
+    <col min="8" max="8" width="8.88671875" style="9"/>
     <col min="9" max="9" width="50" style="9" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>108</v>
       </c>
@@ -7233,7 +7285,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>79899</v>
       </c>
@@ -7268,7 +7320,7 @@
         <v>4860276</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>157185</v>
       </c>
@@ -7300,7 +7352,7 @@
         <v>4859994</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>160857</v>
       </c>
@@ -7332,7 +7384,7 @@
         <v>4786064</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>160611</v>
       </c>
@@ -7364,7 +7416,7 @@
         <v>4826475</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>159240</v>
       </c>
@@ -7396,7 +7448,7 @@
         <v>4870165</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>160582</v>
       </c>
@@ -7431,7 +7483,7 @@
         <v>4870238</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>160591</v>
       </c>
@@ -7463,7 +7515,7 @@
         <v>4891523</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>27816</v>
       </c>
@@ -7498,7 +7550,7 @@
         <v>4775607</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>28743</v>
       </c>
@@ -7524,7 +7576,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>160562</v>
       </c>
@@ -7559,7 +7611,7 @@
         <v>4907342</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>30303</v>
       </c>
@@ -7594,7 +7646,7 @@
         <v>4878594</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>108280</v>
       </c>
@@ -7617,7 +7669,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>29233</v>
       </c>
@@ -7652,7 +7704,7 @@
         <v>4812405</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>29492</v>
       </c>
@@ -7687,7 +7739,7 @@
         <v>4790196</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>160650</v>
       </c>
@@ -7722,7 +7774,7 @@
         <v>4799940</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>160649</v>
       </c>
@@ -7757,7 +7809,7 @@
         <v>4801321</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>29479</v>
       </c>
@@ -7792,7 +7844,7 @@
         <v>4797116</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>160756</v>
       </c>
@@ -7827,7 +7879,7 @@
         <v>4800099</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>160755</v>
       </c>
@@ -7862,7 +7914,7 @@
         <v>4791093</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>29475</v>
       </c>
@@ -7897,7 +7949,7 @@
         <v>4792369</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>160006</v>
       </c>
@@ -7932,7 +7984,7 @@
         <v>4826476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>160004</v>
       </c>
@@ -7964,7 +8016,7 @@
         <v>4835756</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>135876</v>
       </c>
@@ -7990,7 +8042,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>160780</v>
       </c>
@@ -8025,7 +8077,7 @@
         <v>4890307</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>160809</v>
       </c>
@@ -8057,7 +8109,7 @@
         <v>4830337</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -8089,7 +8141,7 @@
         <v>4832159</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>160015</v>
       </c>
@@ -8121,7 +8173,7 @@
         <v>4872295</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>161036</v>
       </c>
@@ -8144,7 +8196,7 @@
         <v>280</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="K29">
         <v>396166</v>
@@ -8153,7 +8205,7 @@
         <v>4849503</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>161109</v>
       </c>
@@ -8185,7 +8237,7 @@
         <v>4849030</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>28548</v>
       </c>
@@ -8220,7 +8272,7 @@
         <v>4845290</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>29779</v>
       </c>
@@ -8252,7 +8304,7 @@
         <v>4779348</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -8284,7 +8336,7 @@
         <v>4835206</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>130340</v>
       </c>
@@ -8316,7 +8368,7 @@
         <v>4817544</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>148485</v>
       </c>
@@ -8345,7 +8397,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>161289</v>
       </c>
@@ -8374,7 +8426,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>47890</v>
       </c>
@@ -8397,7 +8449,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>161454</v>
       </c>
@@ -8429,7 +8481,7 @@
         <v>4831304</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>161489</v>
       </c>
@@ -8461,7 +8513,7 @@
         <v>4781541</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>29375</v>
       </c>
@@ -8493,7 +8545,7 @@
         <v>4811371</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>29188</v>
       </c>
@@ -8525,7 +8577,7 @@
         <v>4799999</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>29528</v>
       </c>
@@ -8560,7 +8612,7 @@
         <v>4801214</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>29478</v>
       </c>
@@ -8595,7 +8647,7 @@
         <v>4803297</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>29477</v>
       </c>
@@ -8627,7 +8679,7 @@
         <v>4799769</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -8650,7 +8702,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
         <v>29366</v>
       </c>
@@ -8682,7 +8734,7 @@
         <v>4835279</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="12">
         <v>162131</v>
       </c>
@@ -8717,7 +8769,7 @@
         <v>4813926</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="12">
         <v>29265</v>
       </c>
@@ -8749,7 +8801,7 @@
         <v>4815750</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="12">
         <v>29589</v>
       </c>
@@ -8784,7 +8836,7 @@
         <v>4834619</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -8819,7 +8871,7 @@
         <v>4883797</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>162043</v>
       </c>
@@ -8851,7 +8903,7 @@
         <v>4792480</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>29309</v>
       </c>
@@ -8883,7 +8935,7 @@
         <v>4792035</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>29228</v>
       </c>
@@ -8915,7 +8967,7 @@
         <v>4781316</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>27754</v>
       </c>
@@ -8950,7 +9002,7 @@
         <v>4822782</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>28558</v>
       </c>
@@ -8961,7 +9013,7 @@
         <v>465</v>
       </c>
       <c r="D55" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E55" t="s">
         <v>361</v>
@@ -8982,7 +9034,7 @@
         <v>4876452</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>89</v>
       </c>
@@ -9014,7 +9066,7 @@
         <v>4883303</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>29167</v>
       </c>
@@ -9043,7 +9095,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>27761</v>
       </c>
@@ -9075,7 +9127,7 @@
         <v>4825020</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>32302</v>
       </c>
@@ -9107,7 +9159,7 @@
         <v>4775528</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>37326</v>
       </c>
@@ -9133,7 +9185,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>101259</v>
       </c>
@@ -9165,7 +9217,7 @@
         <v>4775800</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -9188,7 +9240,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>89</v>
       </c>
@@ -9214,7 +9266,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>29028</v>
       </c>
@@ -9249,7 +9301,7 @@
         <v>4857362</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>29502</v>
       </c>
@@ -9281,7 +9333,7 @@
         <v>4847881</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>30603</v>
       </c>
@@ -9316,7 +9368,7 @@
         <v>4900013</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>35046</v>
       </c>
@@ -9351,11 +9403,11 @@
         <v>5223901</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>163169</v>
       </c>
-      <c r="B68" s="39" t="s">
+      <c r="B68" s="38" t="s">
         <v>569</v>
       </c>
       <c r="C68" s="13" t="s">
@@ -9383,7 +9435,7 @@
         <v>4810541</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>29471</v>
       </c>
@@ -9415,7 +9467,7 @@
         <v>4793468</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>29527</v>
       </c>
@@ -9450,7 +9502,7 @@
         <v>4802852</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>30798</v>
       </c>
@@ -9482,7 +9534,7 @@
         <v>4808719</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>29643</v>
       </c>
@@ -9514,7 +9566,7 @@
         <v>4849718</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>56098</v>
       </c>
@@ -9522,10 +9574,10 @@
         <v>600</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D73" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E73" t="s">
         <v>120</v>
@@ -9549,7 +9601,7 @@
         <v>4843461</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>28261</v>
       </c>
@@ -9584,7 +9636,7 @@
         <v>4853638</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>163289</v>
       </c>
@@ -9616,7 +9668,7 @@
         <v>4876511</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>163318</v>
       </c>
@@ -9648,7 +9700,7 @@
         <v>4849053</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>163351</v>
       </c>
@@ -9665,7 +9717,7 @@
         <v>128</v>
       </c>
       <c r="F77" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G77" s="11" t="s">
         <v>659</v>
@@ -9680,7 +9732,7 @@
         <v>4934714</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>163349</v>
       </c>
@@ -9697,7 +9749,7 @@
         <v>128</v>
       </c>
       <c r="F78" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G78" s="11" t="s">
         <v>663</v>
@@ -9715,7 +9767,7 @@
         <v>4932388</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>163350</v>
       </c>
@@ -9732,7 +9784,7 @@
         <v>128</v>
       </c>
       <c r="F79" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G79" s="11" t="s">
         <v>662</v>
@@ -9750,7 +9802,7 @@
         <v>4932115</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>163353</v>
       </c>
@@ -9767,7 +9819,7 @@
         <v>128</v>
       </c>
       <c r="F80" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G80" s="11" t="s">
         <v>665</v>
@@ -9785,7 +9837,7 @@
         <v>4927177</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>163354</v>
       </c>
@@ -9802,7 +9854,7 @@
         <v>128</v>
       </c>
       <c r="F81" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G81" s="11" t="s">
         <v>666</v>
@@ -9820,7 +9872,7 @@
         <v>4934971</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>163352</v>
       </c>
@@ -9837,7 +9889,7 @@
         <v>128</v>
       </c>
       <c r="F82" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G82" s="11" t="s">
         <v>667</v>
@@ -9852,7 +9904,7 @@
         <v>4941779</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>89</v>
       </c>
@@ -9863,7 +9915,7 @@
         <v>672</v>
       </c>
       <c r="D83" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="E83" t="s">
         <v>226</v>
@@ -9875,7 +9927,7 @@
         <v>674</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="K83">
         <v>373564</v>
@@ -9884,7 +9936,7 @@
         <v>4843390</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>27155</v>
       </c>
@@ -9916,7 +9968,7 @@
         <v>4826133</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>29726</v>
       </c>
@@ -9948,7 +10000,7 @@
         <v>4844292</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>29538</v>
       </c>
@@ -9956,7 +10008,7 @@
         <v>462</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D86" t="s">
         <v>89</v>
@@ -9968,7 +10020,7 @@
         <v>517</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="K86">
         <v>373423</v>
@@ -9977,15 +10029,15 @@
         <v>4817038</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>28307</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D87" t="s">
         <v>89</v>
@@ -9994,13 +10046,13 @@
         <v>128</v>
       </c>
       <c r="F87" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="K87">
         <v>417730</v>
@@ -10009,15 +10061,15 @@
         <v>4856673</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>162169</v>
       </c>
       <c r="B88" s="17" t="s">
+        <v>713</v>
+      </c>
+      <c r="C88" s="13" t="s">
         <v>715</v>
-      </c>
-      <c r="C88" s="13" t="s">
-        <v>717</v>
       </c>
       <c r="D88" t="s">
         <v>89</v>
@@ -10026,13 +10078,13 @@
         <v>128</v>
       </c>
       <c r="F88" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="K88">
         <v>429527</v>
@@ -10041,7 +10093,7 @@
         <v>4861811</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>89</v>
       </c>
@@ -10049,7 +10101,7 @@
         <v>439</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D89" t="s">
         <v>89</v>
@@ -10061,7 +10113,7 @@
         <v>456</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="K89">
         <v>358757</v>
@@ -10070,7 +10122,7 @@
         <v>4790414</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -10078,19 +10130,19 @@
         <v>225</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D90" t="s">
+        <v>726</v>
+      </c>
+      <c r="E90" t="s">
+        <v>727</v>
+      </c>
+      <c r="F90" t="s">
         <v>728</v>
       </c>
-      <c r="E90" t="s">
+      <c r="H90" s="11" t="s">
         <v>729</v>
-      </c>
-      <c r="F90" t="s">
-        <v>730</v>
-      </c>
-      <c r="H90" s="11" t="s">
-        <v>731</v>
       </c>
       <c r="K90">
         <v>395766</v>
@@ -10099,7 +10151,7 @@
         <v>4831685</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>89</v>
       </c>
@@ -10107,10 +10159,10 @@
         <v>671</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D91" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="E91" t="s">
         <v>226</v>
@@ -10119,7 +10171,7 @@
         <v>673</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="K91">
         <v>370364</v>
@@ -10128,7 +10180,7 @@
         <v>4848956</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>89</v>
       </c>
@@ -10136,10 +10188,10 @@
         <v>671</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D92" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="E92" t="s">
         <v>226</v>
@@ -10148,7 +10200,7 @@
         <v>673</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="K92">
         <v>369839</v>
@@ -10157,7 +10209,7 @@
         <v>4848992</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -10165,7 +10217,7 @@
         <v>636</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D93" t="s">
         <v>89</v>
@@ -10177,10 +10229,10 @@
         <v>456</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="K93">
         <v>386078</v>
@@ -10189,12 +10241,12 @@
         <v>4851266</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>28947</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C94" s="17" t="s">
         <v>450</v>
@@ -10209,10 +10261,10 @@
         <v>456</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="K94">
         <v>368660</v>
@@ -10221,7 +10273,7 @@
         <v>4885278</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>27355</v>
       </c>
@@ -10229,7 +10281,7 @@
         <v>204</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D95" t="s">
         <v>89</v>
@@ -10238,13 +10290,13 @@
         <v>128</v>
       </c>
       <c r="F95" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="K95">
         <v>383498</v>
@@ -10253,7 +10305,7 @@
         <v>4841926</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>28824</v>
       </c>
@@ -10261,7 +10313,7 @@
         <v>204</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D96" t="s">
         <v>89</v>
@@ -10270,13 +10322,13 @@
         <v>128</v>
       </c>
       <c r="F96" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="H96" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="K96">
         <v>381140</v>
@@ -10285,15 +10337,15 @@
         <v>4843550</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>29331</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D97" t="s">
         <v>89</v>
@@ -10305,7 +10357,7 @@
         <v>456</v>
       </c>
       <c r="H97" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="J97" t="s">
         <v>530</v>
@@ -10317,7 +10369,7 @@
         <v>4871254</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>28251</v>
       </c>
@@ -10325,7 +10377,7 @@
         <v>636</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D98" t="s">
         <v>89</v>
@@ -10334,13 +10386,13 @@
         <v>128</v>
       </c>
       <c r="F98" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="K98">
         <v>384636</v>
@@ -10349,7 +10401,7 @@
         <v>4850998</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>29307</v>
       </c>
@@ -10357,7 +10409,7 @@
         <v>439</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="D99" t="s">
         <v>89</v>
@@ -10366,10 +10418,10 @@
         <v>128</v>
       </c>
       <c r="F99" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="K99">
         <v>352211</v>
@@ -10378,7 +10430,7 @@
         <v>4798488</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>89</v>
       </c>
@@ -10386,7 +10438,7 @@
         <v>671</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D100" t="s">
         <v>89</v>
@@ -10398,13 +10450,33 @@
         <v>673</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="K100">
         <v>372038</v>
       </c>
       <c r="L100">
         <v>4843249</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" s="41">
+        <v>64926</v>
+      </c>
+      <c r="B101" s="17" t="s">
+        <v>785</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>788</v>
+      </c>
+      <c r="D101" s="41" t="s">
+        <v>786</v>
+      </c>
+      <c r="E101" t="s">
+        <v>339</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>787</v>
       </c>
     </row>
   </sheetData>
@@ -10416,21 +10488,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85FB2797-7499-48A9-92FB-AF4E9D955C63}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="65" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>110</v>
       </c>
@@ -10462,7 +10534,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -10494,7 +10566,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -10526,7 +10598,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -10558,7 +10630,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -10590,7 +10662,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>589</v>
       </c>
@@ -10622,7 +10694,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>589</v>
       </c>
@@ -10654,7 +10726,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>589</v>
       </c>
@@ -10686,7 +10758,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -10718,7 +10790,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -10750,7 +10822,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -10782,7 +10854,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -10814,7 +10886,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -10846,7 +10918,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -10878,7 +10950,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -10910,7 +10982,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -10942,7 +11014,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -10950,7 +11022,7 @@
         <v>400</v>
       </c>
       <c r="C17" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D17" t="s">
         <v>308</v>
@@ -10974,7 +11046,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -11006,7 +11078,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -11038,7 +11110,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -11070,7 +11142,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>235</v>
       </c>
@@ -11102,7 +11174,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>238</v>
       </c>
@@ -11134,7 +11206,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>240</v>
       </c>
@@ -11166,7 +11238,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>332</v>
       </c>
@@ -11198,7 +11270,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>372</v>
       </c>
@@ -11230,7 +11302,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>476</v>
       </c>
@@ -11262,7 +11334,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>576</v>
       </c>
@@ -11294,7 +11366,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>621</v>
       </c>
@@ -11326,9 +11398,9 @@
         <v>625</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B29" t="s">
         <v>610</v>
@@ -11358,7 +11430,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>642</v>
       </c>
@@ -11372,7 +11444,7 @@
         <v>640</v>
       </c>
       <c r="E30" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="F30" t="s">
         <v>643</v>
@@ -11390,7 +11462,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>642</v>
       </c>
@@ -11422,21 +11494,21 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>532</v>
       </c>
       <c r="B32" t="s">
+        <v>702</v>
+      </c>
+      <c r="C32" t="s">
+        <v>704</v>
+      </c>
+      <c r="D32" t="s">
         <v>703</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>705</v>
-      </c>
-      <c r="D32" t="s">
-        <v>704</v>
-      </c>
-      <c r="E32" t="s">
-        <v>706</v>
       </c>
       <c r="F32" t="s">
         <v>89</v>
@@ -11681,18 +11753,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11715,18 +11787,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E629FC-C0A0-418E-A068-5110321EDDA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9CEC6D-B35B-412B-B4C7-0CC920F4535C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E629FC-C0A0-418E-A068-5110321EDDA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/lookup/Spill_lab_tracking.xlsx
+++ b/lookup/Spill_lab_tracking.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/refactor/lookup/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas.Beem\OneDrive - State of Maine\Documents\refactor\lookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2002" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4265AB0E-99B5-46B2-A702-058D04E22A09}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="456" windowWidth="19668" windowHeight="11136" activeTab="1" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
+    <workbookView xWindow="-23025" yWindow="2145" windowWidth="21600" windowHeight="11100" activeTab="1" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
@@ -3047,24 +3047,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9741DC-F95F-47C4-8FE8-2842B1A8CB0D}">
   <dimension ref="A1:L147"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.88671875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="16" customWidth="1"/>
-    <col min="5" max="5" width="4.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="16" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" style="1" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" customWidth="1"/>
     <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" style="23"/>
-    <col min="12" max="12" width="11.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.109375" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="23"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="7" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="K1" s="37"/>
     </row>
-    <row r="2" spans="1:11" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>98</v>
       </c>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="K2" s="37"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>98</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>98</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>98</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>98</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>432</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>432</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>98</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>66</v>
       </c>
@@ -3418,7 +3418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>98</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>589</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>589</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>589</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>589</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>11</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>86</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>86</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>86</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>29</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>18</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>589</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>589</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>50</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>62</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>63</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>66</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>66</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>66</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>73</v>
       </c>
@@ -4250,7 +4250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>62</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>63</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>62</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>11</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>11</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>11</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>86</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>86</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>86</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>332</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>332</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>29</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>589</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>32</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>49</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>63</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>73</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>66</v>
       </c>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="L55" s="15"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>62</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>50</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>11</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>11</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>11</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>476</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>476</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>86</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>589</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>32</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>86</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>86</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>63</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>66</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>216</v>
       </c>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="K70"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>216</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>219</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>220</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>218</v>
       </c>
@@ -5442,7 +5442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>345</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>213</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>213</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>213</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>213</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>211</v>
       </c>
@@ -5634,7 +5634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>211</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>217</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>217</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>217</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>217</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>29</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>11</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>11</v>
       </c>
@@ -5890,7 +5890,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>11</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>62</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>576</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>50</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>32</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>461</v>
       </c>
@@ -6082,7 +6082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>461</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>461</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>621</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>710</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>710</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>710</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>86</v>
       </c>
@@ -6306,7 +6306,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>86</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>86</v>
       </c>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="K103"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>642</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>642</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>642</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>642</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>63</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>66</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>642</v>
       </c>
@@ -6598,7 +6598,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>642</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>73</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>711</v>
       </c>
@@ -6697,7 +6697,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>621</v>
       </c>
@@ -6729,7 +6729,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>642</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>769</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>642</v>
       </c>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="J117" s="4"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>642</v>
       </c>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="J118" s="4"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>642</v>
       </c>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="J119" s="4"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>642</v>
       </c>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="J120" s="4"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
       <c r="B121" s="30"/>
       <c r="D121" s="34"/>
@@ -6924,7 +6924,7 @@
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
       <c r="B122" s="30"/>
       <c r="D122" s="34"/>
@@ -6935,7 +6935,7 @@
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="3"/>
       <c r="B123" s="30"/>
       <c r="D123" s="34"/>
@@ -6946,7 +6946,7 @@
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
       <c r="B124" s="30"/>
       <c r="D124" s="34"/>
@@ -6957,7 +6957,7 @@
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
       <c r="B125" s="30"/>
       <c r="D125" s="34"/>
@@ -6968,7 +6968,7 @@
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
       <c r="B126" s="30"/>
       <c r="D126" s="34"/>
@@ -6979,7 +6979,7 @@
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
       <c r="B127" s="30"/>
       <c r="D127" s="34"/>
@@ -6990,7 +6990,7 @@
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="3"/>
       <c r="B128" s="30"/>
       <c r="D128" s="34"/>
@@ -7001,7 +7001,7 @@
       <c r="I128" s="4"/>
       <c r="J128" s="4"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
       <c r="B129" s="30"/>
       <c r="D129" s="34"/>
@@ -7012,7 +7012,7 @@
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
       <c r="B130" s="30"/>
       <c r="D130" s="34"/>
@@ -7023,7 +7023,7 @@
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
       <c r="B131" s="30"/>
       <c r="D131" s="34"/>
@@ -7034,7 +7034,7 @@
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
       <c r="B132" s="30"/>
       <c r="D132" s="34"/>
@@ -7045,7 +7045,7 @@
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="3"/>
       <c r="B133" s="30"/>
       <c r="D133" s="34"/>
@@ -7056,7 +7056,7 @@
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="3"/>
       <c r="B134" s="30"/>
       <c r="D134" s="34"/>
@@ -7067,7 +7067,7 @@
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="3"/>
       <c r="B135" s="30"/>
       <c r="D135" s="34"/>
@@ -7078,7 +7078,7 @@
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="3"/>
       <c r="B136" s="30"/>
       <c r="D136" s="34"/>
@@ -7089,7 +7089,7 @@
       <c r="I136" s="4"/>
       <c r="J136" s="4"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="3"/>
       <c r="B137" s="30"/>
       <c r="D137" s="34"/>
@@ -7100,7 +7100,7 @@
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="3"/>
       <c r="B138" s="30"/>
       <c r="D138" s="34"/>
@@ -7111,7 +7111,7 @@
       <c r="I138" s="4"/>
       <c r="J138" s="4"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="3"/>
       <c r="B139" s="30"/>
       <c r="D139" s="34"/>
@@ -7122,7 +7122,7 @@
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="3"/>
       <c r="B140" s="30"/>
       <c r="D140" s="34"/>
@@ -7133,7 +7133,7 @@
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="3"/>
       <c r="B141" s="30"/>
       <c r="D141" s="34"/>
@@ -7144,7 +7144,7 @@
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="3"/>
       <c r="B142" s="30"/>
       <c r="D142" s="34"/>
@@ -7155,7 +7155,7 @@
       <c r="I142" s="4"/>
       <c r="J142" s="4"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="3"/>
       <c r="B143" s="30"/>
       <c r="D143" s="34"/>
@@ -7166,7 +7166,7 @@
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="3"/>
       <c r="B144" s="30"/>
       <c r="D144" s="34"/>
@@ -7177,7 +7177,7 @@
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="3"/>
       <c r="B145" s="30"/>
       <c r="D145" s="34"/>
@@ -7188,7 +7188,7 @@
       <c r="I145" s="4"/>
       <c r="J145" s="4"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="3"/>
       <c r="B146" s="30"/>
       <c r="D146" s="34"/>
@@ -7199,7 +7199,7 @@
       <c r="I146" s="4"/>
       <c r="J146" s="4"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="3"/>
       <c r="B147" s="30"/>
       <c r="D147" s="34"/>
@@ -7233,21 +7233,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05C0069-E32D-47E3-8952-41BB91A7FDEB}">
   <dimension ref="A1:L101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="11"/>
-    <col min="8" max="8" width="8.88671875" style="9"/>
+    <col min="5" max="5" width="7.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="11"/>
+    <col min="8" max="8" width="8.85546875" style="9"/>
     <col min="9" max="9" width="50" style="9" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>108</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>79899</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>4860276</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>157185</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>4859994</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>160857</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>4786064</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>160611</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>4826475</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>159240</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>4870165</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>160582</v>
       </c>
@@ -7483,7 +7483,7 @@
         <v>4870238</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>160591</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>4891523</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>27816</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>4775607</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>28743</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>160562</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>4907342</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>30303</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>4878594</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>108280</v>
       </c>
@@ -7669,7 +7669,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>29233</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>4812405</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>29492</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>4790196</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>160650</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>4799940</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>160649</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>4801321</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>29479</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>4797116</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>160756</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>4800099</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>160755</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>4791093</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>29475</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>4792369</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>160006</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>4826476</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>160004</v>
       </c>
@@ -8016,7 +8016,7 @@
         <v>4835756</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>135876</v>
       </c>
@@ -8042,7 +8042,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>160780</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>4890307</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>160809</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>4830337</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>4832159</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>160015</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>4872295</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>161036</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>4849503</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>161109</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>4849030</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28548</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>4845290</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29779</v>
       </c>
@@ -8304,7 +8304,7 @@
         <v>4779348</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -8336,7 +8336,7 @@
         <v>4835206</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>130340</v>
       </c>
@@ -8368,7 +8368,7 @@
         <v>4817544</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>148485</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>161289</v>
       </c>
@@ -8426,7 +8426,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>47890</v>
       </c>
@@ -8449,7 +8449,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>161454</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>4831304</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>161489</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>4781541</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>29375</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>4811371</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>29188</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>4799999</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>29528</v>
       </c>
@@ -8612,7 +8612,7 @@
         <v>4801214</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>29478</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>4803297</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>29477</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>4799769</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <v>29366</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>4835279</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <v>162131</v>
       </c>
@@ -8769,7 +8769,7 @@
         <v>4813926</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <v>29265</v>
       </c>
@@ -8801,7 +8801,7 @@
         <v>4815750</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <v>29589</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>4834619</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -8871,7 +8871,7 @@
         <v>4883797</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>162043</v>
       </c>
@@ -8903,7 +8903,7 @@
         <v>4792480</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>29309</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>4792035</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>29228</v>
       </c>
@@ -8967,7 +8967,7 @@
         <v>4781316</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>27754</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>4822782</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>28558</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>4876452</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>89</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>4883303</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>29167</v>
       </c>
@@ -9095,7 +9095,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>27761</v>
       </c>
@@ -9127,7 +9127,7 @@
         <v>4825020</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>32302</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>4775528</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>37326</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>101259</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>4775800</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>89</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>29028</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>4857362</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>29502</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>4847881</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>30603</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>4900013</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>35046</v>
       </c>
@@ -9403,7 +9403,7 @@
         <v>5223901</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>163169</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>4810541</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>29471</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>4793468</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>29527</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>4802852</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>30798</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>4808719</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>29643</v>
       </c>
@@ -9566,7 +9566,7 @@
         <v>4849718</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>56098</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>4843461</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>28261</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>4853638</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>163289</v>
       </c>
@@ -9668,7 +9668,7 @@
         <v>4876511</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>163318</v>
       </c>
@@ -9700,7 +9700,7 @@
         <v>4849053</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>163351</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>4934714</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>163349</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>4932388</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>163350</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>4932115</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>163353</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>4927177</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>163354</v>
       </c>
@@ -9872,7 +9872,7 @@
         <v>4934971</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>163352</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>4941779</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>89</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>4843390</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>27155</v>
       </c>
@@ -9968,7 +9968,7 @@
         <v>4826133</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>29726</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>4844292</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>29538</v>
       </c>
@@ -10029,7 +10029,7 @@
         <v>4817038</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>28307</v>
       </c>
@@ -10061,7 +10061,7 @@
         <v>4856673</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>162169</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>4861811</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>89</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>4790414</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>4831685</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>89</v>
       </c>
@@ -10180,7 +10180,7 @@
         <v>4848956</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>89</v>
       </c>
@@ -10209,7 +10209,7 @@
         <v>4848992</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -10241,7 +10241,7 @@
         <v>4851266</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>28947</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>4885278</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>27355</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>4841926</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>28824</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>4843550</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>29331</v>
       </c>
@@ -10369,7 +10369,7 @@
         <v>4871254</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>28251</v>
       </c>
@@ -10401,7 +10401,7 @@
         <v>4850998</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>29307</v>
       </c>
@@ -10430,7 +10430,7 @@
         <v>4798488</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>89</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>4843249</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="41">
         <v>64926</v>
       </c>
@@ -10488,21 +10488,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85FB2797-7499-48A9-92FB-AF4E9D955C63}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="65" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>110</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -10566,7 +10566,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>86</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>589</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>589</v>
       </c>
@@ -10726,7 +10726,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>589</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -10790,7 +10790,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -10854,7 +10854,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -10886,7 +10886,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -11014,7 +11014,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -11046,7 +11046,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -11078,7 +11078,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
@@ -11110,7 +11110,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>235</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>238</v>
       </c>
@@ -11206,7 +11206,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>240</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>332</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>372</v>
       </c>
@@ -11302,7 +11302,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>476</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>576</v>
       </c>
@@ -11366,7 +11366,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>621</v>
       </c>
@@ -11398,7 +11398,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>700</v>
       </c>
@@ -11430,7 +11430,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>642</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>642</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>532</v>
       </c>
@@ -11753,18 +11753,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11787,18 +11787,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E629FC-C0A0-418E-A068-5110321EDDA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9CEC6D-B35B-412B-B4C7-0CC920F4535C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E629FC-C0A0-418E-A068-5110321EDDA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/lookup/Spill_lab_tracking.xlsx
+++ b/lookup/Spill_lab_tracking.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas.Beem\OneDrive - State of Maine\Documents\refactor\lookup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/refactor/lookup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2002" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4265AB0E-99B5-46B2-A702-058D04E22A09}"/>
+  <xr:revisionPtr revIDLastSave="2013" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48CAA3A6-F7F9-4842-8263-5CD87C0600B9}"/>
   <bookViews>
-    <workbookView xWindow="-23025" yWindow="2145" windowWidth="21600" windowHeight="11100" activeTab="1" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
+    <workbookView xWindow="-23025" yWindow="2145" windowWidth="21600" windowHeight="11100" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="789">
   <si>
     <t>Durham</t>
   </si>
@@ -187,9 +187,6 @@
     <t>L2533459-01</t>
   </si>
   <si>
-    <t>Laflemme</t>
-  </si>
-  <si>
     <t>Lane</t>
   </si>
   <si>
@@ -2405,6 +2402,9 @@
   </si>
   <si>
     <t>Chase Bank</t>
+  </si>
+  <si>
+    <t>808base</t>
   </si>
 </sst>
 </file>
@@ -3099,13 +3099,13 @@
     </row>
     <row r="2" spans="1:11" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>103</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>104</v>
       </c>
       <c r="D2" s="33">
         <v>45877</v>
@@ -3132,13 +3132,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D3" s="34">
         <v>45538</v>
@@ -3164,13 +3164,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B4" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="D4" s="34">
         <v>45847</v>
@@ -3196,13 +3196,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="D5" s="34">
         <v>45540</v>
@@ -3228,13 +3228,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="34">
         <v>45924</v>
@@ -3260,13 +3260,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D7" s="34">
         <v>45538</v>
@@ -3292,13 +3292,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>436</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="D8" s="34">
         <v>45540</v>
@@ -3324,13 +3324,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9" s="34">
         <v>45540</v>
@@ -3359,7 +3359,7 @@
         <v>32</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>36</v>
@@ -3388,13 +3388,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D11" s="34">
         <v>45747</v>
@@ -3420,13 +3420,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" s="34">
         <v>45747</v>
@@ -3452,13 +3452,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="D13" s="34">
         <v>45583</v>
@@ -3484,7 +3484,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B14" s="30" t="s">
         <v>43</v>
@@ -3519,7 +3519,7 @@
         <v>29</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>35</v>
@@ -3548,7 +3548,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B16" s="30" t="s">
         <v>44</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B17" s="30" t="s">
         <v>42</v>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B18" s="30" t="s">
         <v>41</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="30" t="s">
         <v>48</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="30" t="s">
         <v>39</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B24" s="30" t="s">
         <v>40</v>
@@ -3839,7 +3839,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>35</v>
@@ -3871,7 +3871,7 @@
         <v>32</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>36</v>
@@ -3903,7 +3903,7 @@
         <v>18</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>37</v>
@@ -3935,7 +3935,7 @@
         <v>18</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>38</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>15</v>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>14</v>
@@ -4028,13 +4028,13 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="34">
         <v>45833</v>
@@ -4060,13 +4060,13 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D32" s="34">
         <v>45835</v>
@@ -4092,13 +4092,13 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D33" s="34">
         <v>45841</v>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D34" s="34">
         <v>45845</v>
@@ -4156,13 +4156,13 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D35" s="34">
         <v>45845</v>
@@ -4188,13 +4188,13 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D36" s="34">
         <v>45845</v>
@@ -4220,13 +4220,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D37" s="34">
         <v>45846</v>
@@ -4252,13 +4252,13 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D38" s="34">
         <v>45852</v>
@@ -4284,13 +4284,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D39" s="34">
         <v>45859</v>
@@ -4316,13 +4316,13 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D40" s="34">
         <v>45874</v>
@@ -4351,7 +4351,7 @@
         <v>11</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>16</v>
@@ -4383,7 +4383,7 @@
         <v>11</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>17</v>
@@ -4415,7 +4415,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
@@ -4444,10 +4444,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>26</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>25</v>
@@ -4508,10 +4508,10 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>23</v>
@@ -4540,13 +4540,13 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D47" s="34">
         <v>45908</v>
@@ -4572,13 +4572,13 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D48" s="34">
         <v>45908</v>
@@ -4607,7 +4607,7 @@
         <v>29</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>35</v>
@@ -4636,10 +4636,10 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B50" s="30" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>14</v>
@@ -4671,7 +4671,7 @@
         <v>32</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>36</v>
@@ -4700,10 +4700,10 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>49</v>
+        <v>588</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>15</v>
@@ -4732,13 +4732,13 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D53" s="34">
         <v>45939</v>
@@ -4764,13 +4764,13 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D54" s="34">
         <v>45947</v>
@@ -4796,13 +4796,13 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D55" s="34">
         <v>45947</v>
@@ -4829,13 +4829,13 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D56" s="34">
         <v>45968</v>
@@ -4861,13 +4861,13 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D57" s="34">
         <v>45978</v>
@@ -4896,7 +4896,7 @@
         <v>11</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>16</v>
@@ -4928,7 +4928,7 @@
         <v>11</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>17</v>
@@ -4960,7 +4960,7 @@
         <v>11</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>21</v>
@@ -4987,18 +4987,18 @@
         <v>7</v>
       </c>
       <c r="K60" s="23" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D61" s="34">
         <v>45995</v>
@@ -5022,18 +5022,18 @@
         <v>7</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B62" s="30" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D62" s="34">
         <v>45995</v>
@@ -5059,10 +5059,10 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>23</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>15</v>
@@ -5126,7 +5126,7 @@
         <v>32</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>36</v>
@@ -5155,10 +5155,10 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>26</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>25</v>
@@ -5219,13 +5219,13 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D68" s="34">
         <v>46042</v>
@@ -5251,13 +5251,13 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D69" s="34">
         <v>46035</v>
@@ -5283,13 +5283,13 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D70" s="35">
         <v>45869</v>
@@ -5316,13 +5316,13 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D71" s="21">
         <v>45855</v>
@@ -5348,13 +5348,13 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B72" s="24" t="s">
+        <v>538</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="D72" s="34">
         <v>45966</v>
@@ -5380,13 +5380,13 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B73" s="24" t="s">
+        <v>542</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>543</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>544</v>
       </c>
       <c r="D73" s="34">
         <v>45862</v>
@@ -5412,13 +5412,13 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D74" s="39">
         <v>45918</v>
@@ -5444,13 +5444,13 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B75" s="24" t="s">
+        <v>545</v>
+      </c>
+      <c r="C75" s="36" t="s">
         <v>546</v>
-      </c>
-      <c r="C75" s="36" t="s">
-        <v>547</v>
       </c>
       <c r="D75" s="39">
         <v>45966</v>
@@ -5476,13 +5476,13 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D76" s="16">
         <v>45981.384722222225</v>
@@ -5508,13 +5508,13 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D77" s="16">
         <v>45981.384722222225</v>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D78" s="16">
         <v>45981.384722222225</v>
@@ -5572,13 +5572,13 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D79" s="16">
         <v>45981.384722222225</v>
@@ -5604,13 +5604,13 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D80" s="16">
         <v>45975.356944444444</v>
@@ -5636,13 +5636,13 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="D81" s="16">
         <v>45975.356944444444</v>
@@ -5668,13 +5668,13 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B82" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="D82" s="16">
         <v>45930.490277777775</v>
@@ -5700,13 +5700,13 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D83" s="16">
         <v>45944.458333333336</v>
@@ -5732,13 +5732,13 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D84" s="16">
         <v>45944.458333333336</v>
@@ -5764,13 +5764,13 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="D85" s="16">
         <v>45965.449305555558</v>
@@ -5799,7 +5799,7 @@
         <v>29</v>
       </c>
       <c r="B86" s="30" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>35</v>
@@ -5831,7 +5831,7 @@
         <v>11</v>
       </c>
       <c r="B87" s="30" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>17</v>
@@ -5863,7 +5863,7 @@
         <v>11</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>16</v>
@@ -5895,7 +5895,7 @@
         <v>11</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>21</v>
@@ -5924,13 +5924,13 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D90" s="34">
         <v>46091</v>
@@ -5956,13 +5956,13 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B91" s="30" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D91" s="34">
         <v>46091</v>
@@ -5988,13 +5988,13 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B92" s="30" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D92" s="34">
         <v>46092</v>
@@ -6023,7 +6023,7 @@
         <v>32</v>
       </c>
       <c r="B93" s="30" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>36</v>
@@ -6052,13 +6052,13 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B94" s="30" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D94" s="34">
         <v>46003</v>
@@ -6084,13 +6084,13 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B95" s="30" t="s">
+        <v>607</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>609</v>
       </c>
       <c r="D95" s="34">
         <v>46003</v>
@@ -6116,13 +6116,13 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D96" s="34">
         <v>46000</v>
@@ -6148,13 +6148,13 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D97" s="34">
         <v>46119</v>
@@ -6180,13 +6180,13 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B98" s="30" t="s">
+        <v>683</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>685</v>
       </c>
       <c r="D98" s="34">
         <v>46120</v>
@@ -6212,13 +6212,13 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B99" s="30" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D99" s="34">
         <v>46120</v>
@@ -6244,13 +6244,13 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D100" s="34">
         <v>46121</v>
@@ -6276,13 +6276,13 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B101" s="30" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D101" s="34">
         <v>46121</v>
@@ -6308,13 +6308,13 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B102" s="30" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D102" s="34">
         <v>46121</v>
@@ -6340,13 +6340,13 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D103" s="34">
         <v>46121</v>
@@ -6373,13 +6373,13 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B104" s="30" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D104" s="34">
         <v>46125</v>
@@ -6405,13 +6405,13 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B105" s="30" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D105" s="34">
         <v>46125</v>
@@ -6437,13 +6437,13 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B106" s="30" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D106" s="34">
         <v>46135</v>
@@ -6469,13 +6469,13 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B107" s="30" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D107" s="34">
         <v>46135</v>
@@ -6501,13 +6501,13 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B108" s="30" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D108" s="34">
         <v>46136</v>
@@ -6533,13 +6533,13 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B109" s="30" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D109" s="34">
         <v>46146</v>
@@ -6560,21 +6560,21 @@
         <v>7</v>
       </c>
       <c r="J109" s="40" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K109" s="23" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B110" s="30" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D110" s="34">
         <v>46101</v>
@@ -6600,13 +6600,13 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B111" s="30" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D111" s="34">
         <v>46150</v>
@@ -6632,13 +6632,13 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B112" s="30" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D112" s="34">
         <v>46150</v>
@@ -6664,13 +6664,13 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B113" s="30" t="s">
+        <v>718</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>719</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>720</v>
       </c>
       <c r="D113" s="34">
         <v>46147</v>
@@ -6688,24 +6688,24 @@
         <v>7</v>
       </c>
       <c r="I113" s="40" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="J113" s="40" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K113" s="23" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B114" s="30" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D114" s="34">
         <v>46212</v>
@@ -6731,13 +6731,13 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B115" s="30" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D115" s="34">
         <v>46135</v>
@@ -6763,13 +6763,13 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="B116" s="30" t="s">
         <v>769</v>
       </c>
-      <c r="B116" s="30" t="s">
-        <v>770</v>
-      </c>
       <c r="C116" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D116" s="34">
         <v>46233</v>
@@ -6795,13 +6795,13 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B117" s="30" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D117" s="34">
         <v>46237</v>
@@ -6825,13 +6825,13 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B118" s="30" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D118" s="34">
         <v>46237</v>
@@ -6855,13 +6855,13 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B119" s="30" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D119" s="34">
         <v>46237</v>
@@ -6885,13 +6885,13 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B120" s="30" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D120" s="34">
         <v>46237</v>
@@ -6914,10 +6914,19 @@
       <c r="J120" s="4"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="3"/>
+      <c r="A121" s="3" t="s">
+        <v>588</v>
+      </c>
       <c r="B121" s="30"/>
-      <c r="D121" s="34"/>
-      <c r="E121" s="4"/>
+      <c r="C121" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D121" s="34">
+        <v>46262</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="F121" s="4"/>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
@@ -6925,10 +6934,19 @@
       <c r="J121" s="4"/>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="3"/>
+      <c r="A122" s="3" t="s">
+        <v>588</v>
+      </c>
       <c r="B122" s="30"/>
-      <c r="D122" s="34"/>
-      <c r="E122" s="4"/>
+      <c r="C122" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="D122" s="34">
+        <v>46262</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
@@ -7249,40 +7267,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s">
         <v>108</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>109</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>110</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>111</v>
       </c>
-      <c r="E1" t="s">
-        <v>112</v>
-      </c>
       <c r="F1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G1" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="J1" t="s">
+        <v>528</v>
+      </c>
+      <c r="K1" t="s">
+        <v>587</v>
+      </c>
+      <c r="L1" t="s">
         <v>529</v>
-      </c>
-      <c r="K1" t="s">
-        <v>588</v>
-      </c>
-      <c r="L1" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -7290,28 +7308,28 @@
         <v>79899</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G2" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>126</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>127</v>
       </c>
       <c r="K2">
         <v>401693</v>
@@ -7325,25 +7343,25 @@
         <v>157185</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="F3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>129</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="K3">
         <v>401698</v>
@@ -7357,25 +7375,25 @@
         <v>160857</v>
       </c>
       <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
         <v>64</v>
       </c>
-      <c r="C4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" t="s">
-        <v>65</v>
-      </c>
       <c r="E4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>131</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>132</v>
       </c>
       <c r="K4">
         <v>363342</v>
@@ -7392,22 +7410,22 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G5" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="K5">
         <v>370823</v>
@@ -7424,22 +7442,22 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G6" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>159</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>160</v>
       </c>
       <c r="K6">
         <v>409829</v>
@@ -7462,19 +7480,19 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="J7" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K7">
         <v>355651</v>
@@ -7497,16 +7515,16 @@
         <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K8">
         <v>362562</v>
@@ -7520,28 +7538,28 @@
         <v>27816</v>
       </c>
       <c r="B9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" t="s">
+        <v>413</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C9" t="s">
-        <v>200</v>
-      </c>
-      <c r="D9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F9" t="s">
-        <v>414</v>
-      </c>
-      <c r="G9" s="11" t="s">
+      <c r="H9" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="K9">
         <v>357422</v>
@@ -7555,25 +7573,25 @@
         <v>28743</v>
       </c>
       <c r="B10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" t="s">
+        <v>413</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" t="s">
-        <v>120</v>
-      </c>
-      <c r="F10" t="s">
-        <v>414</v>
-      </c>
-      <c r="G10" s="11" t="s">
+      <c r="H10" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -7581,28 +7599,28 @@
         <v>160562</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
         <v>73</v>
       </c>
-      <c r="D11" t="s">
-        <v>74</v>
-      </c>
       <c r="E11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F11" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G11" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>246</v>
-      </c>
       <c r="J11" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K11">
         <v>381249</v>
@@ -7616,28 +7634,28 @@
         <v>30303</v>
       </c>
       <c r="B12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G12" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>248</v>
-      </c>
       <c r="J12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K12">
         <v>460486</v>
@@ -7651,22 +7669,22 @@
         <v>108280</v>
       </c>
       <c r="B13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -7674,28 +7692,28 @@
         <v>29233</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F14" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G14" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>251</v>
-      </c>
       <c r="J14" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K14">
         <v>370438</v>
@@ -7709,28 +7727,28 @@
         <v>29492</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G15" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>253</v>
-      </c>
       <c r="J15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K15">
         <v>354977</v>
@@ -7744,28 +7762,28 @@
         <v>160650</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G16" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>255</v>
-      </c>
       <c r="J16" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K16">
         <v>364381</v>
@@ -7779,28 +7797,28 @@
         <v>160649</v>
       </c>
       <c r="B17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" t="s">
         <v>215</v>
       </c>
-      <c r="C17" t="s">
-        <v>216</v>
-      </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G17" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>257</v>
-      </c>
       <c r="J17" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K17">
         <v>363794</v>
@@ -7814,28 +7832,28 @@
         <v>29479</v>
       </c>
       <c r="B18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F18" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J18" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K18">
         <v>362846</v>
@@ -7849,28 +7867,28 @@
         <v>160756</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F19" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G19" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="J19" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K19">
         <v>364380</v>
@@ -7884,28 +7902,28 @@
         <v>160755</v>
       </c>
       <c r="B20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F20" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J20" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K20">
         <v>365715</v>
@@ -7919,28 +7937,28 @@
         <v>29475</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F21" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G21" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="9" t="s">
-        <v>265</v>
-      </c>
       <c r="J21" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K21">
         <v>366642</v>
@@ -7963,19 +7981,19 @@
         <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F22" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G22" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>267</v>
-      </c>
       <c r="J22" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K22">
         <v>342465</v>
@@ -7998,16 +8016,16 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F23" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K23">
         <v>341365</v>
@@ -8021,25 +8039,25 @@
         <v>135876</v>
       </c>
       <c r="B24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" t="s">
+        <v>220</v>
+      </c>
+      <c r="D24" t="s">
         <v>222</v>
       </c>
-      <c r="C24" t="s">
-        <v>221</v>
-      </c>
-      <c r="D24" t="s">
-        <v>223</v>
-      </c>
       <c r="E24" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G24" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="H24" s="9" t="s">
         <v>270</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -8047,28 +8065,28 @@
         <v>160780</v>
       </c>
       <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" t="s">
         <v>51</v>
       </c>
-      <c r="C25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" t="s">
-        <v>52</v>
-      </c>
       <c r="E25" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F25" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G25" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="H25" s="9" t="s">
-        <v>273</v>
-      </c>
       <c r="J25" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K25">
         <v>356983</v>
@@ -8082,25 +8100,25 @@
         <v>160809</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F26" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K26">
         <v>362128</v>
@@ -8111,28 +8129,28 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B27" t="s">
+        <v>224</v>
+      </c>
+      <c r="C27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D27" t="s">
+        <v>495</v>
+      </c>
+      <c r="E27" t="s">
         <v>225</v>
       </c>
-      <c r="C27" t="s">
-        <v>224</v>
-      </c>
-      <c r="D27" t="s">
-        <v>496</v>
-      </c>
-      <c r="E27" t="s">
-        <v>226</v>
-      </c>
       <c r="F27" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G27" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="H27" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="K27">
         <v>396106</v>
@@ -8146,25 +8164,25 @@
         <v>160015</v>
       </c>
       <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
         <v>67</v>
       </c>
-      <c r="C28" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" t="s">
-        <v>68</v>
-      </c>
       <c r="E28" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F28" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G28" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="H28" s="9" t="s">
         <v>278</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>279</v>
       </c>
       <c r="K28">
         <v>386967</v>
@@ -8178,25 +8196,25 @@
         <v>161036</v>
       </c>
       <c r="B29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F29" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="K29">
         <v>396166</v>
@@ -8210,25 +8228,25 @@
         <v>161109</v>
       </c>
       <c r="B30" t="s">
+        <v>227</v>
+      </c>
+      <c r="C30" t="s">
         <v>228</v>
       </c>
-      <c r="C30" t="s">
-        <v>229</v>
-      </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F30" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K30">
         <v>402042</v>
@@ -8242,28 +8260,28 @@
         <v>28548</v>
       </c>
       <c r="B31" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C31" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J31" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K31">
         <v>396531</v>
@@ -8277,25 +8295,25 @@
         <v>29779</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K32">
         <v>359563</v>
@@ -8306,28 +8324,28 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F33" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K33">
         <v>398815</v>
@@ -8341,25 +8359,25 @@
         <v>130340</v>
       </c>
       <c r="B34" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" t="s">
         <v>234</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>235</v>
       </c>
-      <c r="D34" t="s">
-        <v>236</v>
-      </c>
       <c r="E34" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G34" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="H34" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>289</v>
       </c>
       <c r="K34">
         <v>388074</v>
@@ -8373,28 +8391,28 @@
         <v>148485</v>
       </c>
       <c r="B35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" t="s">
         <v>237</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>238</v>
       </c>
-      <c r="D35" t="s">
-        <v>239</v>
-      </c>
       <c r="E35" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J35" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -8402,28 +8420,28 @@
         <v>161289</v>
       </c>
       <c r="B36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C36" t="s">
+        <v>239</v>
+      </c>
+      <c r="D36" t="s">
         <v>240</v>
       </c>
-      <c r="D36" t="s">
-        <v>241</v>
-      </c>
       <c r="E36" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G36" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="H36" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>293</v>
-      </c>
       <c r="J36" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -8431,22 +8449,22 @@
         <v>47890</v>
       </c>
       <c r="B37" t="s">
+        <v>241</v>
+      </c>
+      <c r="C37" t="s">
         <v>242</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>243</v>
       </c>
-      <c r="D37" t="s">
-        <v>244</v>
-      </c>
       <c r="E37" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -8454,25 +8472,25 @@
         <v>161454</v>
       </c>
       <c r="B38" t="s">
+        <v>330</v>
+      </c>
+      <c r="C38" t="s">
         <v>331</v>
       </c>
-      <c r="C38" t="s">
-        <v>332</v>
-      </c>
       <c r="D38" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E38" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J38" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K38">
         <v>374983</v>
@@ -8486,25 +8504,25 @@
         <v>161489</v>
       </c>
       <c r="B39" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C39" t="s">
+        <v>581</v>
+      </c>
+      <c r="D39" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" t="s">
+        <v>127</v>
+      </c>
+      <c r="F39" t="s">
+        <v>455</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>583</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>582</v>
-      </c>
-      <c r="D39" t="s">
-        <v>89</v>
-      </c>
-      <c r="E39" t="s">
-        <v>128</v>
-      </c>
-      <c r="F39" t="s">
-        <v>456</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>583</v>
       </c>
       <c r="K39">
         <v>353342</v>
@@ -8518,25 +8536,25 @@
         <v>29375</v>
       </c>
       <c r="B40" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C40" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F40" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K40">
         <v>373284</v>
@@ -8550,25 +8568,25 @@
         <v>29188</v>
       </c>
       <c r="B41" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" t="s">
+        <v>350</v>
+      </c>
+      <c r="D41" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" t="s">
+        <v>455</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>351</v>
-      </c>
-      <c r="D41" t="s">
-        <v>89</v>
-      </c>
-      <c r="E41" t="s">
-        <v>128</v>
-      </c>
-      <c r="F41" t="s">
-        <v>456</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>352</v>
       </c>
       <c r="K41">
         <v>354755</v>
@@ -8582,28 +8600,28 @@
         <v>29528</v>
       </c>
       <c r="B42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C42" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F42" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J42" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K42">
         <v>371842</v>
@@ -8617,28 +8635,28 @@
         <v>29478</v>
       </c>
       <c r="B43" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F43" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J43" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K43">
         <v>369943</v>
@@ -8652,25 +8670,25 @@
         <v>29477</v>
       </c>
       <c r="B44" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C44" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F44" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K44">
         <v>373513</v>
@@ -8681,25 +8699,25 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B45" t="s">
+        <v>362</v>
+      </c>
+      <c r="C45" t="s">
         <v>363</v>
       </c>
-      <c r="C45" t="s">
-        <v>364</v>
-      </c>
       <c r="D45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E45" t="s">
+        <v>360</v>
+      </c>
+      <c r="F45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G45" s="11" t="s">
         <v>361</v>
-      </c>
-      <c r="F45" t="s">
-        <v>89</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -8707,25 +8725,25 @@
         <v>29366</v>
       </c>
       <c r="B46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K46">
         <v>379385</v>
@@ -8739,28 +8757,28 @@
         <v>162131</v>
       </c>
       <c r="B47" t="s">
+        <v>414</v>
+      </c>
+      <c r="C47" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>416</v>
-      </c>
       <c r="D47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F47" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J47" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K47">
         <v>372461</v>
@@ -8774,25 +8792,25 @@
         <v>29265</v>
       </c>
       <c r="B48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F48" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K48">
         <v>373157</v>
@@ -8806,28 +8824,28 @@
         <v>29589</v>
       </c>
       <c r="B49" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E49" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F49" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J49" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K49">
         <v>380032</v>
@@ -8838,31 +8856,31 @@
     </row>
     <row r="50" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B50" t="s">
+        <v>424</v>
+      </c>
+      <c r="C50" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="D50" t="s">
+        <v>88</v>
+      </c>
+      <c r="E50" t="s">
+        <v>360</v>
+      </c>
+      <c r="F50" t="s">
+        <v>458</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="H50" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="D50" t="s">
-        <v>89</v>
-      </c>
-      <c r="E50" t="s">
-        <v>361</v>
-      </c>
-      <c r="F50" t="s">
-        <v>459</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>429</v>
-      </c>
-      <c r="H50" s="14" t="s">
+      <c r="I50" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>428</v>
       </c>
       <c r="K50">
         <v>404519</v>
@@ -8876,25 +8894,25 @@
         <v>162043</v>
       </c>
       <c r="B51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C51" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="D51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E51" t="s">
+        <v>127</v>
+      </c>
+      <c r="F51" t="s">
+        <v>455</v>
+      </c>
+      <c r="G51" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="D51" t="s">
-        <v>89</v>
-      </c>
-      <c r="E51" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" t="s">
-        <v>456</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>438</v>
-      </c>
       <c r="H51" s="11" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K51">
         <v>367200</v>
@@ -8908,25 +8926,25 @@
         <v>29309</v>
       </c>
       <c r="B52" t="s">
+        <v>438</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>440</v>
-      </c>
       <c r="D52" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E52" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F52" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G52" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="H52" s="9" t="s">
         <v>443</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>444</v>
       </c>
       <c r="K52">
         <v>353467</v>
@@ -8940,25 +8958,25 @@
         <v>29228</v>
       </c>
       <c r="B53" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C53" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="D53" t="s">
+        <v>88</v>
+      </c>
+      <c r="E53" t="s">
+        <v>127</v>
+      </c>
+      <c r="F53" t="s">
+        <v>455</v>
+      </c>
+      <c r="G53" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="D53" t="s">
-        <v>89</v>
-      </c>
-      <c r="E53" t="s">
-        <v>128</v>
-      </c>
-      <c r="F53" t="s">
-        <v>456</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>442</v>
-      </c>
       <c r="H53" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K53">
         <v>353814</v>
@@ -8972,28 +8990,28 @@
         <v>27754</v>
       </c>
       <c r="B54" t="s">
+        <v>461</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="D54" t="s">
+        <v>682</v>
+      </c>
+      <c r="E54" t="s">
+        <v>119</v>
+      </c>
+      <c r="F54" t="s">
+        <v>413</v>
+      </c>
+      <c r="G54" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>462</v>
-      </c>
-      <c r="D54" t="s">
-        <v>683</v>
-      </c>
-      <c r="E54" t="s">
-        <v>120</v>
-      </c>
-      <c r="F54" t="s">
-        <v>414</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>463</v>
-      </c>
       <c r="H54" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K54">
         <v>369873</v>
@@ -9007,25 +9025,25 @@
         <v>28558</v>
       </c>
       <c r="B55" t="s">
+        <v>463</v>
+      </c>
+      <c r="C55" s="13" t="s">
         <v>464</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="D55" t="s">
+        <v>740</v>
+      </c>
+      <c r="E55" t="s">
+        <v>360</v>
+      </c>
+      <c r="F55" t="s">
         <v>465</v>
       </c>
-      <c r="D55" t="s">
-        <v>741</v>
-      </c>
-      <c r="E55" t="s">
-        <v>361</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="H55" t="s">
         <v>466</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>468</v>
-      </c>
-      <c r="H55" t="s">
-        <v>467</v>
       </c>
       <c r="K55">
         <v>411468</v>
@@ -9036,28 +9054,28 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C56" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="D56" t="s">
+        <v>88</v>
+      </c>
+      <c r="E56" t="s">
+        <v>360</v>
+      </c>
+      <c r="F56" t="s">
+        <v>458</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="H56" s="9" t="s">
         <v>470</v>
-      </c>
-      <c r="D56" t="s">
-        <v>89</v>
-      </c>
-      <c r="E56" t="s">
-        <v>361</v>
-      </c>
-      <c r="F56" t="s">
-        <v>459</v>
-      </c>
-      <c r="G56" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>471</v>
       </c>
       <c r="K56">
         <v>403029</v>
@@ -9071,28 +9089,28 @@
         <v>29167</v>
       </c>
       <c r="B57" t="s">
+        <v>474</v>
+      </c>
+      <c r="C57" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="D57" t="s">
         <v>476</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
+        <v>338</v>
+      </c>
+      <c r="F57" t="s">
+        <v>88</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="E57" t="s">
-        <v>339</v>
-      </c>
-      <c r="F57" t="s">
-        <v>89</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>478</v>
-      </c>
       <c r="J57" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -9106,19 +9124,19 @@
         <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F58" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K58">
         <v>368600</v>
@@ -9132,25 +9150,25 @@
         <v>32302</v>
       </c>
       <c r="B59" t="s">
+        <v>199</v>
+      </c>
+      <c r="C59" t="s">
+        <v>484</v>
+      </c>
+      <c r="D59" t="s">
+        <v>88</v>
+      </c>
+      <c r="E59" t="s">
+        <v>119</v>
+      </c>
+      <c r="F59" t="s">
+        <v>413</v>
+      </c>
+      <c r="G59" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C59" t="s">
-        <v>485</v>
-      </c>
-      <c r="D59" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59" t="s">
-        <v>120</v>
-      </c>
-      <c r="F59" t="s">
-        <v>414</v>
-      </c>
-      <c r="G59" s="11" t="s">
-        <v>201</v>
-      </c>
       <c r="H59" s="9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K59">
         <v>357520</v>
@@ -9164,25 +9182,25 @@
         <v>37326</v>
       </c>
       <c r="B60" t="s">
+        <v>199</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="D60" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" t="s">
+        <v>119</v>
+      </c>
+      <c r="F60" t="s">
+        <v>413</v>
+      </c>
+      <c r="G60" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C60" s="13" t="s">
-        <v>486</v>
-      </c>
-      <c r="D60" t="s">
-        <v>89</v>
-      </c>
-      <c r="E60" t="s">
-        <v>120</v>
-      </c>
-      <c r="F60" t="s">
-        <v>414</v>
-      </c>
-      <c r="G60" s="11" t="s">
-        <v>201</v>
-      </c>
       <c r="H60" s="9" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -9190,25 +9208,25 @@
         <v>101259</v>
       </c>
       <c r="B61" t="s">
+        <v>199</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="D61" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" t="s">
+        <v>119</v>
+      </c>
+      <c r="F61" t="s">
+        <v>413</v>
+      </c>
+      <c r="G61" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="D61" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" t="s">
-        <v>120</v>
-      </c>
-      <c r="F61" t="s">
-        <v>414</v>
-      </c>
-      <c r="G61" s="11" t="s">
-        <v>201</v>
-      </c>
       <c r="H61" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K61">
         <v>358329</v>
@@ -9219,51 +9237,51 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F62" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B63" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E63" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F63" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -9271,28 +9289,28 @@
         <v>29028</v>
       </c>
       <c r="B64" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C64" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="D64" t="s">
+        <v>88</v>
+      </c>
+      <c r="E64" t="s">
+        <v>127</v>
+      </c>
+      <c r="F64" t="s">
+        <v>516</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>520</v>
+      </c>
+      <c r="H64" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="D64" t="s">
-        <v>89</v>
-      </c>
-      <c r="E64" t="s">
-        <v>128</v>
-      </c>
-      <c r="F64" t="s">
-        <v>517</v>
-      </c>
-      <c r="G64" s="11" t="s">
-        <v>521</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>527</v>
-      </c>
       <c r="J64" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K64">
         <v>400440</v>
@@ -9306,25 +9324,25 @@
         <v>29502</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E65" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F65" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K65">
         <v>398643</v>
@@ -9338,28 +9356,28 @@
         <v>30603</v>
       </c>
       <c r="B66" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="C66" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="D66" t="s">
+        <v>88</v>
+      </c>
+      <c r="E66" t="s">
+        <v>127</v>
+      </c>
+      <c r="F66" t="s">
         <v>516</v>
       </c>
-      <c r="D66" t="s">
-        <v>89</v>
-      </c>
-      <c r="E66" t="s">
-        <v>128</v>
-      </c>
-      <c r="F66" t="s">
-        <v>517</v>
-      </c>
       <c r="G66" s="11" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J66" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K66">
         <v>432781</v>
@@ -9373,28 +9391,28 @@
         <v>35046</v>
       </c>
       <c r="B67" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="D67" t="s">
+        <v>532</v>
+      </c>
+      <c r="E67" t="s">
+        <v>339</v>
+      </c>
+      <c r="F67" t="s">
+        <v>88</v>
+      </c>
+      <c r="G67" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="C67" s="13" t="s">
-        <v>532</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="H67" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="E67" t="s">
-        <v>340</v>
-      </c>
-      <c r="F67" t="s">
-        <v>89</v>
-      </c>
-      <c r="G67" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>534</v>
-      </c>
       <c r="J67" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K67">
         <v>506824</v>
@@ -9408,25 +9426,25 @@
         <v>163169</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D68" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E68" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F68" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K68">
         <v>341306</v>
@@ -9440,25 +9458,25 @@
         <v>29471</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C69" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="D69" t="s">
+        <v>88</v>
+      </c>
+      <c r="E69" t="s">
+        <v>127</v>
+      </c>
+      <c r="F69" t="s">
+        <v>455</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>585</v>
-      </c>
-      <c r="D69" t="s">
-        <v>89</v>
-      </c>
-      <c r="E69" t="s">
-        <v>128</v>
-      </c>
-      <c r="F69" t="s">
-        <v>456</v>
-      </c>
-      <c r="G69" s="11" t="s">
-        <v>587</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>586</v>
       </c>
       <c r="K69">
         <v>359087</v>
@@ -9472,28 +9490,28 @@
         <v>29527</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C70" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="D70" t="s">
+        <v>88</v>
+      </c>
+      <c r="E70" t="s">
+        <v>127</v>
+      </c>
+      <c r="F70" t="s">
+        <v>455</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="H70" s="9" t="s">
         <v>592</v>
       </c>
-      <c r="D70" t="s">
-        <v>89</v>
-      </c>
-      <c r="E70" t="s">
-        <v>128</v>
-      </c>
-      <c r="F70" t="s">
-        <v>456</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>594</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>593</v>
-      </c>
       <c r="J70" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K70">
         <v>369689</v>
@@ -9507,25 +9525,25 @@
         <v>30798</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E71" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F71" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K71">
         <v>372694</v>
@@ -9539,25 +9557,25 @@
         <v>29643</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C72" s="13" t="s">
+        <v>595</v>
+      </c>
+      <c r="D72" t="s">
         <v>596</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
+        <v>127</v>
+      </c>
+      <c r="F72" t="s">
+        <v>454</v>
+      </c>
+      <c r="G72" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="E72" t="s">
-        <v>128</v>
-      </c>
-      <c r="F72" t="s">
-        <v>455</v>
-      </c>
-      <c r="G72" s="11" t="s">
+      <c r="H72" s="9" t="s">
         <v>598</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>599</v>
       </c>
       <c r="K72">
         <v>395997</v>
@@ -9571,28 +9589,28 @@
         <v>56098</v>
       </c>
       <c r="B73" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="D73" t="s">
+        <v>737</v>
+      </c>
+      <c r="E73" t="s">
+        <v>119</v>
+      </c>
+      <c r="F73" t="s">
+        <v>413</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="C73" s="13" t="s">
-        <v>710</v>
-      </c>
-      <c r="D73" t="s">
-        <v>738</v>
-      </c>
-      <c r="E73" t="s">
-        <v>120</v>
-      </c>
-      <c r="F73" t="s">
-        <v>414</v>
-      </c>
-      <c r="G73" s="11" t="s">
+      <c r="I73" s="9" t="s">
         <v>602</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="I73" s="9" t="s">
-        <v>603</v>
       </c>
       <c r="K73">
         <v>393163</v>
@@ -9606,28 +9624,28 @@
         <v>28261</v>
       </c>
       <c r="B74" s="17" t="s">
+        <v>610</v>
+      </c>
+      <c r="C74" s="13" t="s">
         <v>611</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="D74" t="s">
+        <v>596</v>
+      </c>
+      <c r="E74" t="s">
+        <v>127</v>
+      </c>
+      <c r="F74" t="s">
+        <v>516</v>
+      </c>
+      <c r="G74" s="11" t="s">
         <v>612</v>
       </c>
-      <c r="D74" t="s">
-        <v>597</v>
-      </c>
-      <c r="E74" t="s">
-        <v>128</v>
-      </c>
-      <c r="F74" t="s">
-        <v>517</v>
-      </c>
-      <c r="G74" s="11" t="s">
-        <v>613</v>
-      </c>
       <c r="H74" s="9" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J74" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K74">
         <v>404975</v>
@@ -9641,25 +9659,25 @@
         <v>163289</v>
       </c>
       <c r="B75" s="17" t="s">
+        <v>619</v>
+      </c>
+      <c r="C75" s="13" t="s">
         <v>620</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="D75" t="s">
+        <v>632</v>
+      </c>
+      <c r="E75" t="s">
+        <v>338</v>
+      </c>
+      <c r="F75" t="s">
+        <v>449</v>
+      </c>
+      <c r="G75" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="D75" t="s">
+      <c r="H75" s="9" t="s">
         <v>633</v>
-      </c>
-      <c r="E75" t="s">
-        <v>339</v>
-      </c>
-      <c r="F75" t="s">
-        <v>450</v>
-      </c>
-      <c r="G75" s="11" t="s">
-        <v>622</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>634</v>
       </c>
       <c r="K75">
         <v>419520</v>
@@ -9673,25 +9691,25 @@
         <v>163318</v>
       </c>
       <c r="B76" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>641</v>
+      </c>
+      <c r="D76" t="s">
         <v>636</v>
       </c>
-      <c r="C76" s="13" t="s">
-        <v>642</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
+        <v>338</v>
+      </c>
+      <c r="F76" t="s">
         <v>637</v>
       </c>
-      <c r="E76" t="s">
-        <v>339</v>
-      </c>
-      <c r="F76" t="s">
-        <v>638</v>
-      </c>
       <c r="G76" s="11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="K76">
         <v>390938</v>
@@ -9705,25 +9723,25 @@
         <v>163351</v>
       </c>
       <c r="B77" s="17" t="s">
+        <v>646</v>
+      </c>
+      <c r="C77" s="13" t="s">
         <v>647</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="D77" t="s">
+        <v>88</v>
+      </c>
+      <c r="E77" t="s">
+        <v>127</v>
+      </c>
+      <c r="F77" t="s">
+        <v>755</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>648</v>
-      </c>
-      <c r="D77" t="s">
-        <v>89</v>
-      </c>
-      <c r="E77" t="s">
-        <v>128</v>
-      </c>
-      <c r="F77" t="s">
-        <v>756</v>
-      </c>
-      <c r="G77" s="11" t="s">
-        <v>659</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>649</v>
       </c>
       <c r="K77">
         <v>384803</v>
@@ -9737,28 +9755,28 @@
         <v>163349</v>
       </c>
       <c r="B78" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="C78" s="13" t="s">
         <v>650</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="D78" t="s">
+        <v>88</v>
+      </c>
+      <c r="E78" t="s">
+        <v>127</v>
+      </c>
+      <c r="F78" t="s">
+        <v>755</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="H78" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="D78" t="s">
-        <v>89</v>
-      </c>
-      <c r="E78" t="s">
-        <v>128</v>
-      </c>
-      <c r="F78" t="s">
-        <v>756</v>
-      </c>
-      <c r="G78" s="11" t="s">
-        <v>663</v>
-      </c>
-      <c r="H78" s="9" t="s">
-        <v>652</v>
-      </c>
       <c r="J78" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K78">
         <v>390311</v>
@@ -9772,28 +9790,28 @@
         <v>163350</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C79" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="D79" t="s">
+        <v>88</v>
+      </c>
+      <c r="E79" t="s">
+        <v>127</v>
+      </c>
+      <c r="F79" t="s">
+        <v>755</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="D79" t="s">
-        <v>89</v>
-      </c>
-      <c r="E79" t="s">
-        <v>128</v>
-      </c>
-      <c r="F79" t="s">
-        <v>756</v>
-      </c>
-      <c r="G79" s="11" t="s">
-        <v>662</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>654</v>
-      </c>
       <c r="J79" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K79">
         <v>387863</v>
@@ -9807,28 +9825,28 @@
         <v>163353</v>
       </c>
       <c r="B80" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>645</v>
+      </c>
+      <c r="D80" t="s">
+        <v>88</v>
+      </c>
+      <c r="E80" t="s">
+        <v>127</v>
+      </c>
+      <c r="F80" t="s">
+        <v>755</v>
+      </c>
+      <c r="G80" s="11" t="s">
         <v>664</v>
       </c>
-      <c r="C80" s="13" t="s">
-        <v>646</v>
-      </c>
-      <c r="D80" t="s">
-        <v>89</v>
-      </c>
-      <c r="E80" t="s">
-        <v>128</v>
-      </c>
-      <c r="F80" t="s">
-        <v>756</v>
-      </c>
-      <c r="G80" s="11" t="s">
-        <v>665</v>
-      </c>
       <c r="H80" s="9" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J80" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K80">
         <v>393450</v>
@@ -9842,28 +9860,28 @@
         <v>163354</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D81" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E81" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F81" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J81" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K81">
         <v>383536</v>
@@ -9877,25 +9895,25 @@
         <v>163352</v>
       </c>
       <c r="B82" s="17" t="s">
+        <v>668</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>655</v>
+      </c>
+      <c r="D82" t="s">
+        <v>88</v>
+      </c>
+      <c r="E82" t="s">
+        <v>127</v>
+      </c>
+      <c r="F82" t="s">
+        <v>755</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="H82" s="9" t="s">
         <v>669</v>
-      </c>
-      <c r="C82" s="13" t="s">
-        <v>656</v>
-      </c>
-      <c r="D82" t="s">
-        <v>89</v>
-      </c>
-      <c r="E82" t="s">
-        <v>128</v>
-      </c>
-      <c r="F82" t="s">
-        <v>756</v>
-      </c>
-      <c r="G82" s="11" t="s">
-        <v>667</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>670</v>
       </c>
       <c r="K82">
         <v>374677</v>
@@ -9906,28 +9924,28 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B83" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="C83" s="13" t="s">
         <v>671</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="D83" t="s">
+        <v>777</v>
+      </c>
+      <c r="E83" t="s">
+        <v>225</v>
+      </c>
+      <c r="F83" t="s">
         <v>672</v>
       </c>
-      <c r="D83" t="s">
-        <v>778</v>
-      </c>
-      <c r="E83" t="s">
-        <v>226</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="G83" s="11" t="s">
         <v>673</v>
       </c>
-      <c r="G83" s="11" t="s">
-        <v>674</v>
-      </c>
       <c r="H83" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="K83">
         <v>373564</v>
@@ -9941,25 +9959,25 @@
         <v>27155</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D84" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E84" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F84" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G84" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="H84" s="9" t="s">
         <v>688</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>689</v>
       </c>
       <c r="K84">
         <v>364744</v>
@@ -9973,25 +9991,25 @@
         <v>29726</v>
       </c>
       <c r="B85" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="C85" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="D85" t="s">
+        <v>88</v>
+      </c>
+      <c r="E85" t="s">
+        <v>127</v>
+      </c>
+      <c r="F85" t="s">
+        <v>516</v>
+      </c>
+      <c r="G85" s="11" t="s">
         <v>692</v>
       </c>
-      <c r="D85" t="s">
-        <v>89</v>
-      </c>
-      <c r="E85" t="s">
-        <v>128</v>
-      </c>
-      <c r="F85" t="s">
-        <v>517</v>
-      </c>
-      <c r="G85" s="11" t="s">
-        <v>693</v>
-      </c>
       <c r="H85" s="9" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="K85">
         <v>386981</v>
@@ -10005,22 +10023,22 @@
         <v>29538</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C86" s="13" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D86" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E86" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F86" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="K86">
         <v>373423</v>
@@ -10034,25 +10052,25 @@
         <v>28307</v>
       </c>
       <c r="B87" s="17" t="s">
+        <v>712</v>
+      </c>
+      <c r="C87" s="13" t="s">
         <v>713</v>
       </c>
-      <c r="C87" s="13" t="s">
-        <v>714</v>
-      </c>
       <c r="D87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E87" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F87" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="K87">
         <v>417730</v>
@@ -10066,25 +10084,25 @@
         <v>162169</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E88" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F88" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="K88">
         <v>429527</v>
@@ -10095,25 +10113,25 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C89" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="D89" t="s">
+        <v>88</v>
+      </c>
+      <c r="E89" t="s">
+        <v>127</v>
+      </c>
+      <c r="F89" t="s">
+        <v>455</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>717</v>
-      </c>
-      <c r="D89" t="s">
-        <v>89</v>
-      </c>
-      <c r="E89" t="s">
-        <v>128</v>
-      </c>
-      <c r="F89" t="s">
-        <v>456</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>718</v>
       </c>
       <c r="K89">
         <v>358757</v>
@@ -10124,25 +10142,25 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D90" t="s">
+        <v>725</v>
+      </c>
+      <c r="E90" t="s">
         <v>726</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>727</v>
       </c>
-      <c r="F90" t="s">
+      <c r="H90" s="11" t="s">
         <v>728</v>
-      </c>
-      <c r="H90" s="11" t="s">
-        <v>729</v>
       </c>
       <c r="K90">
         <v>395766</v>
@@ -10153,25 +10171,25 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D91" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E91" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F91" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K91">
         <v>370364</v>
@@ -10182,25 +10200,25 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D92" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E92" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F92" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K92">
         <v>369839</v>
@@ -10211,28 +10229,28 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C93" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="D93" t="s">
+        <v>88</v>
+      </c>
+      <c r="E93" t="s">
+        <v>127</v>
+      </c>
+      <c r="F93" t="s">
+        <v>455</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>744</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>734</v>
-      </c>
-      <c r="D93" t="s">
-        <v>89</v>
-      </c>
-      <c r="E93" t="s">
-        <v>128</v>
-      </c>
-      <c r="F93" t="s">
-        <v>456</v>
-      </c>
-      <c r="G93" s="11" t="s">
-        <v>745</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>735</v>
       </c>
       <c r="K93">
         <v>386078</v>
@@ -10246,25 +10264,25 @@
         <v>28947</v>
       </c>
       <c r="B94" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>449</v>
+      </c>
+      <c r="D94" t="s">
+        <v>88</v>
+      </c>
+      <c r="E94" t="s">
+        <v>127</v>
+      </c>
+      <c r="F94" t="s">
+        <v>455</v>
+      </c>
+      <c r="G94" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="H94" s="9" t="s">
         <v>736</v>
-      </c>
-      <c r="C94" s="17" t="s">
-        <v>450</v>
-      </c>
-      <c r="D94" t="s">
-        <v>89</v>
-      </c>
-      <c r="E94" t="s">
-        <v>128</v>
-      </c>
-      <c r="F94" t="s">
-        <v>456</v>
-      </c>
-      <c r="G94" s="11" t="s">
-        <v>746</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>737</v>
       </c>
       <c r="K94">
         <v>368660</v>
@@ -10278,25 +10296,25 @@
         <v>27355</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C95" s="13" t="s">
+        <v>742</v>
+      </c>
+      <c r="D95" t="s">
+        <v>88</v>
+      </c>
+      <c r="E95" t="s">
+        <v>127</v>
+      </c>
+      <c r="F95" t="s">
+        <v>756</v>
+      </c>
+      <c r="G95" s="11" t="s">
         <v>743</v>
       </c>
-      <c r="D95" t="s">
-        <v>89</v>
-      </c>
-      <c r="E95" t="s">
-        <v>128</v>
-      </c>
-      <c r="F95" t="s">
-        <v>757</v>
-      </c>
-      <c r="G95" s="11" t="s">
-        <v>744</v>
-      </c>
       <c r="H95" s="9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="K95">
         <v>383498</v>
@@ -10310,25 +10328,25 @@
         <v>28824</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D96" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E96" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F96" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H96" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="K96">
         <v>381140</v>
@@ -10342,25 +10360,25 @@
         <v>29331</v>
       </c>
       <c r="B97" s="17" t="s">
+        <v>748</v>
+      </c>
+      <c r="C97" s="13" t="s">
         <v>749</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="D97" t="s">
+        <v>88</v>
+      </c>
+      <c r="E97" t="s">
+        <v>127</v>
+      </c>
+      <c r="F97" t="s">
+        <v>455</v>
+      </c>
+      <c r="H97" t="s">
         <v>750</v>
       </c>
-      <c r="D97" t="s">
-        <v>89</v>
-      </c>
-      <c r="E97" t="s">
-        <v>128</v>
-      </c>
-      <c r="F97" t="s">
-        <v>456</v>
-      </c>
-      <c r="H97" t="s">
-        <v>751</v>
-      </c>
       <c r="J97" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K97">
         <v>403170</v>
@@ -10374,25 +10392,25 @@
         <v>28251</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C98" s="13" t="s">
+        <v>751</v>
+      </c>
+      <c r="D98" t="s">
+        <v>88</v>
+      </c>
+      <c r="E98" t="s">
+        <v>127</v>
+      </c>
+      <c r="F98" t="s">
+        <v>755</v>
+      </c>
+      <c r="G98" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="H98" s="9" t="s">
         <v>752</v>
-      </c>
-      <c r="D98" t="s">
-        <v>89</v>
-      </c>
-      <c r="E98" t="s">
-        <v>128</v>
-      </c>
-      <c r="F98" t="s">
-        <v>756</v>
-      </c>
-      <c r="G98" s="11" t="s">
-        <v>761</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>753</v>
       </c>
       <c r="K98">
         <v>384636</v>
@@ -10406,22 +10424,22 @@
         <v>29307</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C99" s="13" t="s">
+        <v>771</v>
+      </c>
+      <c r="D99" t="s">
+        <v>88</v>
+      </c>
+      <c r="E99" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" t="s">
         <v>772</v>
       </c>
-      <c r="D99" t="s">
-        <v>89</v>
-      </c>
-      <c r="E99" t="s">
-        <v>128</v>
-      </c>
-      <c r="F99" t="s">
-        <v>773</v>
-      </c>
       <c r="H99" s="9" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K99">
         <v>352211</v>
@@ -10432,25 +10450,25 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D100" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E100" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K100">
         <v>372038</v>
@@ -10464,19 +10482,19 @@
         <v>64926</v>
       </c>
       <c r="B101" s="17" t="s">
+        <v>784</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>787</v>
+      </c>
+      <c r="D101" s="41" t="s">
         <v>785</v>
       </c>
-      <c r="C101" s="13" t="s">
-        <v>788</v>
-      </c>
-      <c r="D101" s="41" t="s">
+      <c r="E101" t="s">
+        <v>338</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>786</v>
-      </c>
-      <c r="E101" t="s">
-        <v>339</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>787</v>
       </c>
     </row>
   </sheetData>
@@ -10504,258 +10522,258 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E1" t="s">
         <v>113</v>
       </c>
-      <c r="D1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>114</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>115</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>116</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>117</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>118</v>
-      </c>
-      <c r="J1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" t="s">
         <v>133</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>134</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" t="s">
         <v>135</v>
       </c>
-      <c r="F2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>136</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" t="s">
         <v>137</v>
-      </c>
-      <c r="I2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3" t="s">
         <v>147</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" t="s">
         <v>148</v>
       </c>
-      <c r="G3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>149</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>150</v>
-      </c>
-      <c r="J3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" t="s">
         <v>152</v>
       </c>
-      <c r="F4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" t="s">
         <v>153</v>
-      </c>
-      <c r="H4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I4" t="s">
-        <v>116</v>
-      </c>
-      <c r="J4" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" t="s">
         <v>155</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>156</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>157</v>
       </c>
-      <c r="H5" t="s">
-        <v>158</v>
-      </c>
       <c r="I5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>588</v>
+      </c>
+      <c r="B6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C6" t="s">
         <v>589</v>
       </c>
-      <c r="B6" t="s">
-        <v>389</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" t="s">
         <v>590</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>161</v>
       </c>
-      <c r="E6" t="s">
-        <v>591</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" t="s">
         <v>162</v>
       </c>
-      <c r="G6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H6" t="s">
-        <v>163</v>
-      </c>
       <c r="I6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" t="s">
         <v>164</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>165</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>166</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I7" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7" t="s">
         <v>167</v>
-      </c>
-      <c r="G7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H7" t="s">
-        <v>163</v>
-      </c>
-      <c r="I7" t="s">
-        <v>150</v>
-      </c>
-      <c r="J7" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F8" t="s">
         <v>380</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" t="s">
         <v>381</v>
-      </c>
-      <c r="G8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" t="s">
-        <v>89</v>
-      </c>
-      <c r="J8" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -10763,31 +10781,31 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" t="s">
         <v>171</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>172</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>173</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>174</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>175</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J9" t="s">
         <v>176</v>
-      </c>
-      <c r="I9" t="s">
-        <v>116</v>
-      </c>
-      <c r="J9" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -10795,31 +10813,31 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" t="s">
         <v>178</v>
       </c>
-      <c r="D10" t="s">
-        <v>185</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>179</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>180</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
+        <v>175</v>
+      </c>
+      <c r="I10" t="s">
         <v>181</v>
       </c>
-      <c r="H10" t="s">
-        <v>176</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>182</v>
-      </c>
-      <c r="J10" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -10827,31 +10845,31 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E11" t="s">
         <v>186</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>187</v>
       </c>
-      <c r="F11" t="s">
-        <v>188</v>
-      </c>
       <c r="G11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -10859,31 +10877,31 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" t="s">
         <v>190</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>191</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>192</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" t="s">
+        <v>175</v>
+      </c>
+      <c r="I12" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" t="s">
         <v>193</v>
-      </c>
-      <c r="G12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H12" t="s">
-        <v>176</v>
-      </c>
-      <c r="I12" t="s">
-        <v>89</v>
-      </c>
-      <c r="J12" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -10891,63 +10909,63 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C13" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" t="s">
         <v>195</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>196</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>197</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" t="s">
         <v>198</v>
       </c>
-      <c r="G13" t="s">
-        <v>89</v>
-      </c>
-      <c r="H13" t="s">
-        <v>199</v>
-      </c>
       <c r="I13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C14" t="s">
+        <v>294</v>
+      </c>
+      <c r="D14" t="s">
+        <v>430</v>
+      </c>
+      <c r="E14" t="s">
         <v>295</v>
       </c>
-      <c r="D14" t="s">
-        <v>431</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>296</v>
       </c>
-      <c r="F14" t="s">
-        <v>297</v>
-      </c>
       <c r="G14" t="s">
+        <v>298</v>
+      </c>
+      <c r="H14" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" t="s">
         <v>299</v>
-      </c>
-      <c r="H14" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" t="s">
-        <v>89</v>
-      </c>
-      <c r="J14" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -10955,31 +10973,31 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D15" t="s">
         <v>301</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>302</v>
       </c>
-      <c r="E15" t="s">
-        <v>303</v>
-      </c>
       <c r="F15" t="s">
+        <v>482</v>
+      </c>
+      <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" t="s">
+        <v>175</v>
+      </c>
+      <c r="I15" t="s">
+        <v>149</v>
+      </c>
+      <c r="J15" t="s">
         <v>483</v>
-      </c>
-      <c r="G15" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" t="s">
-        <v>176</v>
-      </c>
-      <c r="I15" t="s">
-        <v>150</v>
-      </c>
-      <c r="J15" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -10987,278 +11005,278 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C16" t="s">
+        <v>303</v>
+      </c>
+      <c r="D16" t="s">
         <v>304</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>305</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>306</v>
       </c>
-      <c r="F16" t="s">
-        <v>307</v>
-      </c>
       <c r="G16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I16" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C17" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D17" t="s">
+        <v>307</v>
+      </c>
+      <c r="E17" t="s">
         <v>308</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>309</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>310</v>
       </c>
-      <c r="G17" t="s">
-        <v>311</v>
-      </c>
       <c r="H17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C18" t="s">
+        <v>410</v>
+      </c>
+      <c r="D18" t="s">
         <v>408</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
+        <v>409</v>
+      </c>
+      <c r="F18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" t="s">
+        <v>88</v>
+      </c>
+      <c r="J18" t="s">
         <v>411</v>
-      </c>
-      <c r="D18" t="s">
-        <v>409</v>
-      </c>
-      <c r="E18" t="s">
-        <v>410</v>
-      </c>
-      <c r="F18" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" t="s">
-        <v>89</v>
-      </c>
-      <c r="J18" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C19" t="s">
+        <v>311</v>
+      </c>
+      <c r="D19" t="s">
         <v>312</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>313</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>314</v>
       </c>
-      <c r="F19" t="s">
-        <v>315</v>
-      </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s">
         <v>28</v>
       </c>
       <c r="I19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C20" t="s">
+        <v>315</v>
+      </c>
+      <c r="D20" t="s">
         <v>316</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>317</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>318</v>
       </c>
-      <c r="F20" t="s">
-        <v>319</v>
-      </c>
       <c r="G20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H20" t="s">
         <v>28</v>
       </c>
       <c r="I20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C21" t="s">
+        <v>319</v>
+      </c>
+      <c r="D21" t="s">
         <v>320</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>321</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>322</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>323</v>
       </c>
-      <c r="G21" t="s">
-        <v>324</v>
-      </c>
       <c r="H21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C22" t="s">
+        <v>336</v>
+      </c>
+      <c r="D22" t="s">
+        <v>324</v>
+      </c>
+      <c r="E22" t="s">
+        <v>376</v>
+      </c>
+      <c r="F22" t="s">
+        <v>325</v>
+      </c>
+      <c r="G22" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" t="s">
+        <v>175</v>
+      </c>
+      <c r="I22" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" t="s">
         <v>337</v>
-      </c>
-      <c r="D22" t="s">
-        <v>325</v>
-      </c>
-      <c r="E22" t="s">
-        <v>377</v>
-      </c>
-      <c r="F22" t="s">
-        <v>326</v>
-      </c>
-      <c r="G22" t="s">
-        <v>89</v>
-      </c>
-      <c r="H22" t="s">
-        <v>176</v>
-      </c>
-      <c r="I22" t="s">
-        <v>89</v>
-      </c>
-      <c r="J22" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C23" t="s">
+        <v>326</v>
+      </c>
+      <c r="D23" t="s">
         <v>327</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>328</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>329</v>
       </c>
-      <c r="F23" t="s">
-        <v>330</v>
-      </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B24" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C24" t="s">
+        <v>334</v>
+      </c>
+      <c r="D24" t="s">
+        <v>364</v>
+      </c>
+      <c r="E24" t="s">
+        <v>365</v>
+      </c>
+      <c r="F24" t="s">
         <v>335</v>
       </c>
-      <c r="D24" t="s">
-        <v>365</v>
-      </c>
-      <c r="E24" t="s">
-        <v>366</v>
-      </c>
-      <c r="F24" t="s">
-        <v>336</v>
-      </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s">
         <v>28</v>
@@ -11267,30 +11285,30 @@
         <v>27</v>
       </c>
       <c r="J24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C25" t="s">
+        <v>369</v>
+      </c>
+      <c r="D25" t="s">
+        <v>367</v>
+      </c>
+      <c r="E25" t="s">
         <v>370</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>368</v>
       </c>
-      <c r="E25" t="s">
-        <v>371</v>
-      </c>
-      <c r="F25" t="s">
-        <v>369</v>
-      </c>
       <c r="G25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s">
         <v>28</v>
@@ -11299,158 +11317,158 @@
         <v>27</v>
       </c>
       <c r="J25" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B26" t="s">
+        <v>489</v>
+      </c>
+      <c r="C26" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" t="s">
         <v>490</v>
       </c>
-      <c r="C26" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" t="s">
         <v>491</v>
       </c>
-      <c r="E26" t="s">
-        <v>89</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" t="s">
+        <v>88</v>
+      </c>
+      <c r="J26" t="s">
         <v>492</v>
-      </c>
-      <c r="G26" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" t="s">
-        <v>89</v>
-      </c>
-      <c r="J26" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>575</v>
+      </c>
+      <c r="B27" t="s">
+        <v>569</v>
+      </c>
+      <c r="C27" t="s">
         <v>576</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
         <v>570</v>
       </c>
-      <c r="C27" t="s">
+      <c r="E27" t="s">
         <v>577</v>
       </c>
-      <c r="D27" t="s">
-        <v>571</v>
-      </c>
-      <c r="E27" t="s">
-        <v>578</v>
-      </c>
       <c r="F27" s="25" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B28" t="s">
+        <v>622</v>
+      </c>
+      <c r="C28" t="s">
+        <v>627</v>
+      </c>
+      <c r="D28" t="s">
+        <v>625</v>
+      </c>
+      <c r="E28" t="s">
+        <v>626</v>
+      </c>
+      <c r="F28" s="26" t="s">
         <v>623</v>
       </c>
-      <c r="C28" t="s">
-        <v>628</v>
-      </c>
-      <c r="D28" t="s">
-        <v>626</v>
-      </c>
-      <c r="E28" t="s">
-        <v>627</v>
-      </c>
-      <c r="F28" s="26" t="s">
+      <c r="G28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" t="s">
+        <v>88</v>
+      </c>
+      <c r="J28" t="s">
         <v>624</v>
-      </c>
-      <c r="G28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28" t="s">
-        <v>89</v>
-      </c>
-      <c r="I28" t="s">
-        <v>89</v>
-      </c>
-      <c r="J28" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B29" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>641</v>
+      </c>
+      <c r="B30" t="s">
+        <v>638</v>
+      </c>
+      <c r="C30" t="s">
+        <v>640</v>
+      </c>
+      <c r="D30" t="s">
+        <v>639</v>
+      </c>
+      <c r="E30" t="s">
+        <v>764</v>
+      </c>
+      <c r="F30" t="s">
         <v>642</v>
       </c>
-      <c r="B30" t="s">
-        <v>639</v>
-      </c>
-      <c r="C30" t="s">
-        <v>641</v>
-      </c>
-      <c r="D30" t="s">
-        <v>640</v>
-      </c>
-      <c r="E30" t="s">
-        <v>765</v>
-      </c>
-      <c r="F30" t="s">
-        <v>643</v>
-      </c>
       <c r="G30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H30" t="s">
         <v>28</v>
@@ -11459,71 +11477,71 @@
         <v>27</v>
       </c>
       <c r="J30" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B31" t="s">
+        <v>659</v>
+      </c>
+      <c r="C31" t="s">
+        <v>677</v>
+      </c>
+      <c r="D31" t="s">
         <v>660</v>
       </c>
-      <c r="C31" t="s">
-        <v>678</v>
-      </c>
-      <c r="D31" t="s">
-        <v>661</v>
-      </c>
       <c r="E31" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F31" t="s">
+        <v>674</v>
+      </c>
+      <c r="G31" s="27" t="s">
         <v>675</v>
       </c>
-      <c r="G31" s="27" t="s">
-        <v>676</v>
-      </c>
       <c r="H31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B32" t="s">
+        <v>701</v>
+      </c>
+      <c r="C32" t="s">
+        <v>703</v>
+      </c>
+      <c r="D32" t="s">
         <v>702</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>704</v>
       </c>
-      <c r="D32" t="s">
-        <v>703</v>
-      </c>
-      <c r="E32" t="s">
-        <v>705</v>
-      </c>
       <c r="F32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -11753,18 +11771,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11787,18 +11805,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E629FC-C0A0-418E-A068-5110321EDDA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9CEC6D-B35B-412B-B4C7-0CC920F4535C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E629FC-C0A0-418E-A068-5110321EDDA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/lookup/Spill_lab_tracking.xlsx
+++ b/lookup/Spill_lab_tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/refactor/lookup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2013" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48CAA3A6-F7F9-4842-8263-5CD87C0600B9}"/>
+  <xr:revisionPtr revIDLastSave="2044" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2369121-68EF-438B-AB4B-48CA83767D2E}"/>
   <bookViews>
-    <workbookView xWindow="-23025" yWindow="2145" windowWidth="21600" windowHeight="11100" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
+    <workbookView xWindow="2850" yWindow="1845" windowWidth="21600" windowHeight="11295" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="793">
   <si>
     <t>Durham</t>
   </si>
@@ -2405,6 +2405,18 @@
   </si>
   <si>
     <t>808base</t>
+  </si>
+  <si>
+    <t>H:\BRWM\PFAS - LD 1600\Sites\Cumberland\Gray Site (Christianson) (EGAD 29271)</t>
+  </si>
+  <si>
+    <t>Gray</t>
+  </si>
+  <si>
+    <t>L2656749-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no reporting </t>
   </si>
 </sst>
 </file>
@@ -6821,7 +6833,9 @@
       <c r="I117" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J117" s="4"/>
+      <c r="J117" s="4" t="s">
+        <v>783</v>
+      </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
@@ -6851,7 +6865,9 @@
       <c r="I118" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J118" s="4"/>
+      <c r="J118" s="4" t="s">
+        <v>783</v>
+      </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
@@ -6881,7 +6897,9 @@
       <c r="I119" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J119" s="4"/>
+      <c r="J119" s="4" t="s">
+        <v>783</v>
+      </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
@@ -6911,7 +6929,9 @@
       <c r="I120" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J120" s="4"/>
+      <c r="J120" s="4" t="s">
+        <v>783</v>
+      </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
@@ -6937,7 +6957,9 @@
       <c r="A122" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="B122" s="30"/>
+      <c r="B122" s="30" t="s">
+        <v>791</v>
+      </c>
       <c r="C122" s="3" t="s">
         <v>788</v>
       </c>
@@ -6947,11 +6969,24 @@
       <c r="E122" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
-      <c r="J122" s="4"/>
+      <c r="F122" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="K122" s="23" t="s">
+        <v>792</v>
+      </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="3"/>
@@ -7250,7 +7285,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05C0069-E32D-47E3-8952-41BB91A7FDEB}">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -10495,6 +10530,35 @@
       </c>
       <c r="H101" s="9" t="s">
         <v>786</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>29271</v>
+      </c>
+      <c r="B102" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>790</v>
+      </c>
+      <c r="D102" t="s">
+        <v>88</v>
+      </c>
+      <c r="E102" t="s">
+        <v>127</v>
+      </c>
+      <c r="F102" t="s">
+        <v>757</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>789</v>
+      </c>
+      <c r="K102">
+        <v>400597</v>
+      </c>
+      <c r="L102">
+        <v>4848180</v>
       </c>
     </row>
   </sheetData>

--- a/lookup/Spill_lab_tracking.xlsx
+++ b/lookup/Spill_lab_tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/refactor/lookup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2044" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2369121-68EF-438B-AB4B-48CA83767D2E}"/>
+  <xr:revisionPtr revIDLastSave="2052" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDCDB360-9545-42E4-8BAC-1CBFF9E04CF3}"/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="1845" windowWidth="21600" windowHeight="11295" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="796">
   <si>
     <t>Durham</t>
   </si>
@@ -2417,6 +2417,15 @@
   </si>
   <si>
     <t xml:space="preserve">no reporting </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Souther Portland </t>
+  </si>
+  <si>
+    <t>Ahold Delhaize</t>
+  </si>
+  <si>
+    <t>Quinn</t>
   </si>
 </sst>
 </file>
@@ -2761,6 +2770,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -7285,7 +7298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05C0069-E32D-47E3-8952-41BB91A7FDEB}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -10559,6 +10572,32 @@
       </c>
       <c r="L102">
         <v>4848180</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>88</v>
+      </c>
+      <c r="B103" s="17" t="s">
+        <v>793</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>794</v>
+      </c>
+      <c r="D103" t="s">
+        <v>596</v>
+      </c>
+      <c r="E103" t="s">
+        <v>726</v>
+      </c>
+      <c r="F103" t="s">
+        <v>795</v>
+      </c>
+      <c r="K103">
+        <v>395950</v>
+      </c>
+      <c r="L103">
+        <v>4830753</v>
       </c>
     </row>
   </sheetData>

--- a/lookup/Spill_lab_tracking.xlsx
+++ b/lookup/Spill_lab_tracking.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/refactor/lookup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2052" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDCDB360-9545-42E4-8BAC-1CBFF9E04CF3}"/>
+  <xr:revisionPtr revIDLastSave="2060" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F77D2C6C-A3F1-4423-807A-7EB639E0ADD6}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
+    <workbookView xWindow="-24135" yWindow="2235" windowWidth="21600" windowHeight="11295" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
     <sheet name="sites" sheetId="7" r:id="rId2"/>
     <sheet name="Contacts" sheetId="8" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028" refMode="R1C1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="798">
   <si>
     <t>Durham</t>
   </si>
@@ -2413,9 +2413,6 @@
     <t>Gray</t>
   </si>
   <si>
-    <t>L2656749-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">no reporting </t>
   </si>
   <si>
@@ -2426,6 +2423,15 @@
   </si>
   <si>
     <t>Quinn</t>
+  </si>
+  <si>
+    <t>L2652862-01</t>
+  </si>
+  <si>
+    <t>esqtr</t>
+  </si>
+  <si>
+    <t>L2656749-01D</t>
   </si>
 </sst>
 </file>
@@ -2770,10 +2776,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -6971,7 +6973,7 @@
         <v>588</v>
       </c>
       <c r="B122" s="30" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>788</v>
@@ -6998,19 +7000,40 @@
         <v>783</v>
       </c>
       <c r="K122" s="23" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="3"/>
-      <c r="B123" s="30"/>
-      <c r="D123" s="34"/>
-      <c r="E123" s="4"/>
-      <c r="F123" s="4"/>
-      <c r="G123" s="4"/>
-      <c r="H123" s="4"/>
-      <c r="I123" s="4"/>
-      <c r="J123" s="4"/>
+      <c r="A123" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B123" s="30" t="s">
+        <v>795</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="D123" s="34">
+        <v>46247</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
@@ -10579,10 +10602,10 @@
         <v>88</v>
       </c>
       <c r="B103" s="17" t="s">
+        <v>792</v>
+      </c>
+      <c r="C103" s="13" t="s">
         <v>793</v>
-      </c>
-      <c r="C103" s="13" t="s">
-        <v>794</v>
       </c>
       <c r="D103" t="s">
         <v>596</v>
@@ -10591,7 +10614,7 @@
         <v>726</v>
       </c>
       <c r="F103" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="K103">
         <v>395950</v>
@@ -11657,6 +11680,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100125872C61801B94CBBE948BC6C9A2B9A" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="68502b0f0955ec7bc8f56677585c1c13">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="83b0043d-3627-4f29-99ea-ed882df73a05" xmlns:ns4="942c1815-1a1b-49ab-ae21-7a54e279a57b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7c7a778c7ed535cdadc2c6f960a471d8" ns3:_="" ns4:_="">
     <xsd:import namespace="83b0043d-3627-4f29-99ea-ed882df73a05"/>
@@ -11873,22 +11911,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E629FC-C0A0-418E-A068-5110321EDDA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9CEC6D-B35B-412B-B4C7-0CC920F4535C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04CEB0DF-FBF6-4FAC-A4B6-1450ADA239FD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11905,21 +11945,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9CEC6D-B35B-412B-B4C7-0CC920F4535C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E629FC-C0A0-418E-A068-5110321EDDA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/lookup/Spill_lab_tracking.xlsx
+++ b/lookup/Spill_lab_tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/refactor/lookup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2060" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F77D2C6C-A3F1-4423-807A-7EB639E0ADD6}"/>
+  <xr:revisionPtr revIDLastSave="2063" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E4FC3BB-8A1A-4C25-A175-A9B6ABDF9E00}"/>
   <bookViews>
-    <workbookView xWindow="-24135" yWindow="2235" windowWidth="21600" windowHeight="11295" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>

--- a/lookup/Spill_lab_tracking.xlsx
+++ b/lookup/Spill_lab_tracking.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofmaine-my.sharepoint.com/personal/lucas_beem_maine_gov/Documents/Documents/refactor/lookup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2063" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E4FC3BB-8A1A-4C25-A175-A9B6ABDF9E00}"/>
+  <xr:revisionPtr revIDLastSave="2074" documentId="13_ncr:1_{4923A7FC-61C1-43DD-ACDC-2AD5F26F4CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57EBF10D-1A7B-4961-BD3D-623461D58D43}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{8A7E386D-9303-4138-8E00-F12B91A17E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="801">
   <si>
     <t>Durham</t>
   </si>
@@ -2432,6 +2432,15 @@
   </si>
   <si>
     <t>L2656749-01D</t>
+  </si>
+  <si>
+    <t>New Glouster</t>
+  </si>
+  <si>
+    <t>H Johnston</t>
+  </si>
+  <si>
+    <t>H:\BRWM\PFAS - LD 1600\Sites\New Gloucester\H Johnston S-021541 New Gloucester</t>
   </si>
 </sst>
 </file>
@@ -7321,7 +7330,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05C0069-E32D-47E3-8952-41BB91A7FDEB}">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
@@ -10608,7 +10617,7 @@
         <v>793</v>
       </c>
       <c r="D103" t="s">
-        <v>596</v>
+        <v>88</v>
       </c>
       <c r="E103" t="s">
         <v>726</v>
@@ -10621,6 +10630,35 @@
       </c>
       <c r="L103">
         <v>4830753</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>29148</v>
+      </c>
+      <c r="B104" s="17" t="s">
+        <v>798</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>799</v>
+      </c>
+      <c r="D104" t="s">
+        <v>88</v>
+      </c>
+      <c r="E104" t="s">
+        <v>127</v>
+      </c>
+      <c r="F104" t="s">
+        <v>755</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="K104">
+        <v>399074</v>
+      </c>
+      <c r="L104">
+        <v>4870081</v>
       </c>
     </row>
   </sheetData>
@@ -11689,12 +11727,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100125872C61801B94CBBE948BC6C9A2B9A" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="68502b0f0955ec7bc8f56677585c1c13">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="83b0043d-3627-4f29-99ea-ed882df73a05" xmlns:ns4="942c1815-1a1b-49ab-ae21-7a54e279a57b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7c7a778c7ed535cdadc2c6f960a471d8" ns3:_="" ns4:_="">
     <xsd:import namespace="83b0043d-3627-4f29-99ea-ed882df73a05"/>
@@ -11911,6 +11943,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80E629FC-C0A0-418E-A068-5110321EDDA0}">
   <ds:schemaRefs>
@@ -11920,15 +11958,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9CEC6D-B35B-412B-B4C7-0CC920F4535C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04CEB0DF-FBF6-4FAC-A4B6-1450ADA239FD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11945,4 +11974,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9CEC6D-B35B-412B-B4C7-0CC920F4535C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>